--- a/tests/traces/h100/facebook_timesformer-base-finetuned-k400__1016002_perf_report.xlsx
+++ b/tests/traces/h100/facebook_timesformer-base-finetuned-k400__1016002_perf_report.xlsx
@@ -1,22 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONV_fwd" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BinaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UnaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Normalization" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="CONV_fwd" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="BinaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="UnaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Normalization" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Reduce_fwd" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="kernel_summary" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="short_kernel_histogram" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="short_kernels_summary" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1739,6 +1743,2739 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AJ2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>param: num_input_elems</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>param: num_output_elems</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>param: dtype_in_out</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>param: reduce_type</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>GFLOPS_first</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Data Moved (MB)_first</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>FLOPS/Byte_first</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_mean</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_median</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_std</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_min</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>TB/s_max</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_mean</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_median</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_std</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_min</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>TFLOPS/s_max</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>process_name_first</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>process_label_first</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>thread_name_first</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Compute Spec</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>kernel_details__summarize_kernel_stats</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>trunc_kernel_details</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Input Dims_first</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Input type_first</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Input Strides_first</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Concrete Inputs_first</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_mean</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_median</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_std</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_min</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_max</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel Time (µs)_sum</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>name_count</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>UID_first</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>aten::mean</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>6144</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', None)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>6.144e-06</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.01172065734863281</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.4999186330349878</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.00226974951117672</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.002259215510277354</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.751008785294355e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.002220059095920617</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.002341823595087458</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.001134690072959298</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.001129423929629297</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.875199184446587e-05</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.001109848908489526</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.001170721250465203</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>thread 17751 (python3)</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;128, 4, at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(64.99300000000001), 'mean_duration_us': np.float64(5.416083333333334), 'median_duration_us': np.float64(5.44), 'std_dev_duration_us': np.float64(0.08484540680293502), 'min_duration_us': np.float64(5.248), 'max_duration_us': np.float64(5.536)}]</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;128, 4, at::native::ReduceOp&lt;c10:...', 'stream': 7, 'mean_duration_us': np.float64(5.42)}]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>[[1, 8, 768], [], [], []]</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'ScalarList', 'Scalar', '']</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>[[19273728, 2409216, 1], [], [], []]</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>['', '[1]', 'True', '']</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>5.416035970052083</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>5.43994140625</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.08856812165190991</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>5.248046875</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>5.535888671875</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>64.992431640625</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>305</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Parent op category</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Parent cpu_op</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel stream</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_sum</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_count</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_mean</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_min</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel duration (µs)_max</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Percent of kernels time (%)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Percent of total time (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>aten::_softmax</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::cunn_SoftMaxForward&lt;8, c10::BFloat16, float, c10::BFloat16, at::native::(anonymous namespace)::SoftMaxForwardEpilogue&gt;(c10::BFloat16*, c10::BFloat16 const*, int)</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2" t="n">
+        <v>68688.625</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5724.052083333333</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5701.537</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5767.809</v>
+      </c>
+      <c r="J2" t="n">
+        <v>44.35656651605</v>
+      </c>
+      <c r="K2" t="n">
+        <v>42.93242273521919</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1&gt;(cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1::Params)</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>43207.642</v>
+      </c>
+      <c r="F3" t="n">
+        <v>24</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1800.318416666667</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1682.295</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1919.478</v>
+      </c>
+      <c r="J3" t="n">
+        <v>27.90189272786689</v>
+      </c>
+      <c r="K3" t="n">
+        <v>27.00605452119636</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>15555.788</v>
+      </c>
+      <c r="F4" t="n">
+        <v>24</v>
+      </c>
+      <c r="G4" t="n">
+        <v>648.1578333333333</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4.896</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1292.505</v>
+      </c>
+      <c r="J4" t="n">
+        <v>10.0453509606805</v>
+      </c>
+      <c r="K4" t="n">
+        <v>9.72282770830614</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8486.164000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>84</v>
+      </c>
+      <c r="G5" t="n">
+        <v>101.0257619047619</v>
+      </c>
+      <c r="H5" t="n">
+        <v>44.992</v>
+      </c>
+      <c r="I5" t="n">
+        <v>165.887</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5.480049978174828</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5.304103557880197</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7378.101</v>
+      </c>
+      <c r="F6" t="n">
+        <v>122</v>
+      </c>
+      <c r="G6" t="n">
+        <v>60.47623770491803</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.944</v>
+      </c>
+      <c r="I6" t="n">
+        <v>154.079</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.764503988377043</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.611531401525994</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NORM_fwd</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>aten::native_layer_norm</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2202.649</v>
+      </c>
+      <c r="F7" t="n">
+        <v>37</v>
+      </c>
+      <c r="G7" t="n">
+        <v>59.53105405405405</v>
+      </c>
+      <c r="H7" t="n">
+        <v>58.815</v>
+      </c>
+      <c r="I7" t="n">
+        <v>60.544</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.422389032827648</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.376720788999748</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>aten::cat</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::CatArrayBatchedCopy_contig&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 128, 1&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 128, 1&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1780.948</v>
+      </c>
+      <c r="F8" t="n">
+        <v>25</v>
+      </c>
+      <c r="G8" t="n">
+        <v>71.23791999999999</v>
+      </c>
+      <c r="H8" t="n">
+        <v>69.983</v>
+      </c>
+      <c r="I8" t="n">
+        <v>72.223</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.150070166983634</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.113145188238127</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>aten::gelu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1534.2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>12</v>
+      </c>
+      <c r="G9" t="n">
+        <v>127.85</v>
+      </c>
+      <c r="H9" t="n">
+        <v>127.103</v>
+      </c>
+      <c r="I9" t="n">
+        <v>128.703</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.9907294599203859</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.9589203883521221</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1360.379</v>
+      </c>
+      <c r="F10" t="n">
+        <v>36</v>
+      </c>
+      <c r="G10" t="n">
+        <v>37.78830555555556</v>
+      </c>
+      <c r="H10" t="n">
+        <v>35.04</v>
+      </c>
+      <c r="I10" t="n">
+        <v>39.936</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.8784823047562473</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.8502771209660224</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>aten::cat</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1302.169</v>
+      </c>
+      <c r="F11" t="n">
+        <v>13</v>
+      </c>
+      <c r="G11" t="n">
+        <v>100.1668461538462</v>
+      </c>
+      <c r="H11" t="n">
+        <v>93.82299999999999</v>
+      </c>
+      <c r="I11" t="n">
+        <v>161.311</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.8408924456362071</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.8138941488594019</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_16x16_32x1_nn_align8&gt;(cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_16x16_32x1_nn_align8::Params)</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1300.504</v>
+      </c>
+      <c r="F12" t="n">
+        <v>12</v>
+      </c>
+      <c r="G12" t="n">
+        <v>108.3753333333333</v>
+      </c>
+      <c r="H12" t="n">
+        <v>107.583</v>
+      </c>
+      <c r="I12" t="n">
+        <v>109.599</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.8398172503873689</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.812853474601413</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CONV_fwd</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>aten::cudnn_convolution</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8&gt;(cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8::Params)</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" t="n">
+        <v>863.099</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>863.099</v>
+      </c>
+      <c r="H13" t="n">
+        <v>863.099</v>
+      </c>
+      <c r="I13" t="n">
+        <v>863.099</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.557357323769929</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.5394624092467268</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>aten::bmm</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>void cutlass::Kernel2&lt;cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_16x16_64x1_nn_align8&gt;(cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_16x16_64x1_nn_align8::Params)</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>7</v>
+      </c>
+      <c r="E14" t="n">
+        <v>490.207</v>
+      </c>
+      <c r="F14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G14" t="n">
+        <v>40.85058333333333</v>
+      </c>
+      <c r="H14" t="n">
+        <v>40.288</v>
+      </c>
+      <c r="I14" t="n">
+        <v>41.632</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.3165574999082209</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.3063938774689928</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CONV_fwd</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>aten::cudnn_convolution</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E15" t="n">
+        <v>291.679</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>145.8395</v>
+      </c>
+      <c r="H15" t="n">
+        <v>10.336</v>
+      </c>
+      <c r="I15" t="n">
+        <v>281.343</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.1883554804719842</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.1823080041416756</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>aten::add</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>7</v>
+      </c>
+      <c r="E16" t="n">
+        <v>140.063</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>70.03149999999999</v>
+      </c>
+      <c r="H16" t="n">
+        <v>53.983</v>
+      </c>
+      <c r="I16" t="n">
+        <v>86.08</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.09044749077358166</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.08754351867668052</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>aten::_softmax</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>void (anonymous namespace)::softmax_warp_forward&lt;c10::BFloat16, c10::BFloat16, float, 3, false, false&gt;(c10::BFloat16*, c10::BFloat16 const*, int, int, int, bool const*, int, bool)</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" t="n">
+        <v>92.672</v>
+      </c>
+      <c r="F17" t="n">
+        <v>12</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7.722666666666666</v>
+      </c>
+      <c r="H17" t="n">
+        <v>7.679</v>
+      </c>
+      <c r="I17" t="n">
+        <v>7.841</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.0598441406007965</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.05792274164344144</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>reduce</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>aten::mean</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>void at::native::reduce_kernel&lt;128, 4, at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" t="n">
+        <v>64.99299999999999</v>
+      </c>
+      <c r="F18" t="n">
+        <v>12</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5.416083333333333</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5.248</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5.536</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.04197006895359512</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.04062254777745369</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>elementwise</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>aten::add_</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>7</v>
+      </c>
+      <c r="E19" t="n">
+        <v>64.864</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>64.864</v>
+      </c>
+      <c r="H19" t="n">
+        <v>64.864</v>
+      </c>
+      <c r="I19" t="n">
+        <v>64.864</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.04188676553791938</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.04054191896106899</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CONV_fwd</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>aten::cudnn_convolution</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>7</v>
+      </c>
+      <c r="E20" t="n">
+        <v>43.488</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>43.488</v>
+      </c>
+      <c r="H20" t="n">
+        <v>43.488</v>
+      </c>
+      <c r="I20" t="n">
+        <v>43.488</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.02808293752640968</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.0271812865654133</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>GEMM</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, false, true, true, false, 7, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;)</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>7</v>
+      </c>
+      <c r="E21" t="n">
+        <v>5.056</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5.056</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5.056</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5.056</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.003264977284159478</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.003160149578613172</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>aten::upsample_nearest1d</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::upsample_nearest1d_out_frame&lt;c10::BFloat16, &amp;at::native::nearest_neighbor_compute_source_index&gt;(c10::BFloat16 const*, unsigned long, unsigned long, unsigned long, unsigned long, c10::BFloat16*, float)</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>7</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.001488483512655775</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.00144069319199038</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>bin_start</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>bin_end</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2.36036</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.36036</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2.41572</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2.41572</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2.47108</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2.47108</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2.52644</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2.52644</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2.5818</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2.5818</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2.63716</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2.63716</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2.69252</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2.69252</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2.74788</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2.74788</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2.80324</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2.80324</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2.8586</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2.8586</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2.91396</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2.91396</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2.96932</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2.96932</v>
+      </c>
+      <c r="B14" t="n">
+        <v>3.02468</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3.02468</v>
+      </c>
+      <c r="B15" t="n">
+        <v>3.08004</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3.08004</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3.1354</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3.1354</v>
+      </c>
+      <c r="B17" t="n">
+        <v>3.19076</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>3.19076</v>
+      </c>
+      <c r="B18" t="n">
+        <v>3.24612</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3.24612</v>
+      </c>
+      <c r="B19" t="n">
+        <v>3.30148</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>3.30148</v>
+      </c>
+      <c r="B20" t="n">
+        <v>3.35684</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>3.35684</v>
+      </c>
+      <c r="B21" t="n">
+        <v>3.4122</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>3.4122</v>
+      </c>
+      <c r="B22" t="n">
+        <v>3.46756</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3.46756</v>
+      </c>
+      <c r="B23" t="n">
+        <v>3.52292</v>
+      </c>
+      <c r="C23" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>3.52292</v>
+      </c>
+      <c r="B24" t="n">
+        <v>3.57828</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>3.57828</v>
+      </c>
+      <c r="B25" t="n">
+        <v>3.63364</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>3.63364</v>
+      </c>
+      <c r="B26" t="n">
+        <v>3.689</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>3.689</v>
+      </c>
+      <c r="B27" t="n">
+        <v>3.74436</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>3.74436</v>
+      </c>
+      <c r="B28" t="n">
+        <v>3.79972</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>3.79972</v>
+      </c>
+      <c r="B29" t="n">
+        <v>3.85508</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>3.85508</v>
+      </c>
+      <c r="B30" t="n">
+        <v>3.91044</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>3.91044</v>
+      </c>
+      <c r="B31" t="n">
+        <v>3.9658</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>3.9658</v>
+      </c>
+      <c r="B32" t="n">
+        <v>4.02116</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>4.02116</v>
+      </c>
+      <c r="B33" t="n">
+        <v>4.07652</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>4.07652</v>
+      </c>
+      <c r="B34" t="n">
+        <v>4.13188</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>4.13188</v>
+      </c>
+      <c r="B35" t="n">
+        <v>4.18724</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>4.18724</v>
+      </c>
+      <c r="B36" t="n">
+        <v>4.242599999999999</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>4.242599999999999</v>
+      </c>
+      <c r="B37" t="n">
+        <v>4.29796</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>4.29796</v>
+      </c>
+      <c r="B38" t="n">
+        <v>4.35332</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>4.35332</v>
+      </c>
+      <c r="B39" t="n">
+        <v>4.40868</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>4.40868</v>
+      </c>
+      <c r="B40" t="n">
+        <v>4.46404</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>4.46404</v>
+      </c>
+      <c r="B41" t="n">
+        <v>4.519399999999999</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>4.519399999999999</v>
+      </c>
+      <c r="B42" t="n">
+        <v>4.574759999999999</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>4.574759999999999</v>
+      </c>
+      <c r="B43" t="n">
+        <v>4.63012</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>4.63012</v>
+      </c>
+      <c r="B44" t="n">
+        <v>4.68548</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>4.68548</v>
+      </c>
+      <c r="B45" t="n">
+        <v>4.74084</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>4.74084</v>
+      </c>
+      <c r="B46" t="n">
+        <v>4.7962</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>4.7962</v>
+      </c>
+      <c r="B47" t="n">
+        <v>4.851559999999999</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>4.851559999999999</v>
+      </c>
+      <c r="B48" t="n">
+        <v>4.90692</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>4.90692</v>
+      </c>
+      <c r="B49" t="n">
+        <v>4.96228</v>
+      </c>
+      <c r="C49" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>4.96228</v>
+      </c>
+      <c r="B50" t="n">
+        <v>5.01764</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>5.01764</v>
+      </c>
+      <c r="B51" t="n">
+        <v>5.073</v>
+      </c>
+      <c r="C51" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>5.073</v>
+      </c>
+      <c r="B52" t="n">
+        <v>5.12836</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>5.12836</v>
+      </c>
+      <c r="B53" t="n">
+        <v>5.183719999999999</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>5.183719999999999</v>
+      </c>
+      <c r="B54" t="n">
+        <v>5.23908</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>5.23908</v>
+      </c>
+      <c r="B55" t="n">
+        <v>5.29444</v>
+      </c>
+      <c r="C55" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>5.29444</v>
+      </c>
+      <c r="B56" t="n">
+        <v>5.3498</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>5.3498</v>
+      </c>
+      <c r="B57" t="n">
+        <v>5.40516</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>5.40516</v>
+      </c>
+      <c r="B58" t="n">
+        <v>5.46052</v>
+      </c>
+      <c r="C58" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>5.46052</v>
+      </c>
+      <c r="B59" t="n">
+        <v>5.515879999999999</v>
+      </c>
+      <c r="C59" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>5.515879999999999</v>
+      </c>
+      <c r="B60" t="n">
+        <v>5.57124</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>5.57124</v>
+      </c>
+      <c r="B61" t="n">
+        <v>5.6266</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>5.6266</v>
+      </c>
+      <c r="B62" t="n">
+        <v>5.68196</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>5.68196</v>
+      </c>
+      <c r="B63" t="n">
+        <v>5.73732</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>5.73732</v>
+      </c>
+      <c r="B64" t="n">
+        <v>5.79268</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>5.79268</v>
+      </c>
+      <c r="B65" t="n">
+        <v>5.848039999999999</v>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>5.848039999999999</v>
+      </c>
+      <c r="B66" t="n">
+        <v>5.9034</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>5.9034</v>
+      </c>
+      <c r="B67" t="n">
+        <v>5.95876</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>5.95876</v>
+      </c>
+      <c r="B68" t="n">
+        <v>6.01412</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>6.01412</v>
+      </c>
+      <c r="B69" t="n">
+        <v>6.06948</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>6.06948</v>
+      </c>
+      <c r="B70" t="n">
+        <v>6.12484</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>6.12484</v>
+      </c>
+      <c r="B71" t="n">
+        <v>6.180199999999999</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>6.180199999999999</v>
+      </c>
+      <c r="B72" t="n">
+        <v>6.23556</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>6.23556</v>
+      </c>
+      <c r="B73" t="n">
+        <v>6.29092</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>6.29092</v>
+      </c>
+      <c r="B74" t="n">
+        <v>6.34628</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>6.34628</v>
+      </c>
+      <c r="B75" t="n">
+        <v>6.40164</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>6.40164</v>
+      </c>
+      <c r="B76" t="n">
+        <v>6.456999999999999</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>6.456999999999999</v>
+      </c>
+      <c r="B77" t="n">
+        <v>6.512359999999999</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>6.512359999999999</v>
+      </c>
+      <c r="B78" t="n">
+        <v>6.56772</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>6.56772</v>
+      </c>
+      <c r="B79" t="n">
+        <v>6.62308</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>6.62308</v>
+      </c>
+      <c r="B80" t="n">
+        <v>6.67844</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>6.67844</v>
+      </c>
+      <c r="B81" t="n">
+        <v>6.733799999999999</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>6.733799999999999</v>
+      </c>
+      <c r="B82" t="n">
+        <v>6.789159999999999</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>6.789159999999999</v>
+      </c>
+      <c r="B83" t="n">
+        <v>6.844519999999999</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>6.844519999999999</v>
+      </c>
+      <c r="B84" t="n">
+        <v>6.89988</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>6.89988</v>
+      </c>
+      <c r="B85" t="n">
+        <v>6.95524</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>6.95524</v>
+      </c>
+      <c r="B86" t="n">
+        <v>7.0106</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>7.0106</v>
+      </c>
+      <c r="B87" t="n">
+        <v>7.065959999999999</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>7.065959999999999</v>
+      </c>
+      <c r="B88" t="n">
+        <v>7.121319999999999</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>7.121319999999999</v>
+      </c>
+      <c r="B89" t="n">
+        <v>7.176679999999999</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>7.176679999999999</v>
+      </c>
+      <c r="B90" t="n">
+        <v>7.23204</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>7.23204</v>
+      </c>
+      <c r="B91" t="n">
+        <v>7.2874</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>7.2874</v>
+      </c>
+      <c r="B92" t="n">
+        <v>7.34276</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>7.34276</v>
+      </c>
+      <c r="B93" t="n">
+        <v>7.398119999999999</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>7.398119999999999</v>
+      </c>
+      <c r="B94" t="n">
+        <v>7.453479999999999</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>7.453479999999999</v>
+      </c>
+      <c r="B95" t="n">
+        <v>7.508839999999999</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>7.508839999999999</v>
+      </c>
+      <c r="B96" t="n">
+        <v>7.5642</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>7.5642</v>
+      </c>
+      <c r="B97" t="n">
+        <v>7.61956</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>7.61956</v>
+      </c>
+      <c r="B98" t="n">
+        <v>7.67492</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>7.67492</v>
+      </c>
+      <c r="B99" t="n">
+        <v>7.730279999999999</v>
+      </c>
+      <c r="C99" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>7.730279999999999</v>
+      </c>
+      <c r="B100" t="n">
+        <v>7.785639999999999</v>
+      </c>
+      <c r="C100" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>7.785639999999999</v>
+      </c>
+      <c r="B101" t="n">
+        <v>7.841</v>
+      </c>
+      <c r="C101" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Parent cpu_op</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Input dims</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Input strides</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Concrete Inputs</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Kernel name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Short Kernel duration (µs) sum</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Short Kernel count</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Short Kernel duration (µs) mean</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Short Kernel duration (µs) percent of total time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>aten::_softmax</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>((3136, 12, 8, 8), (), ())</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>((768, 64, 8, 1), (), ())</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>('', '-1', 'False')</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>void (anonymous namespace)::softmax_warp_forward&lt;c10::BFloat16, c10::BFloat16, float, 3, false, false&gt;(c10::BFloat16*, c10::BFloat16 const*, int, int, int, bool const*, int, bool)</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>92.672</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" t="n">
+        <v>7.722666666666666</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.05792274164344144</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>aten::mean</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>((1, 8, 768), (), (), ())</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>((19273728, 2409216, 1), (), (), ())</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>('', '[1]', 'True', '')</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>void at::native::reduce_kernel&lt;128, 4, at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>64.99299999999999</v>
+      </c>
+      <c r="G3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5.416083333333333</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.04062254777745369</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>aten::mul</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>((3136, 12, 8, 8), ())</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>((768, 64, 8, 1), ())</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>('', '')</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>60.544</v>
+      </c>
+      <c r="G4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5.045333333333333</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.03784179115655773</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>((1, 8, 1, 1, 1, 768), (1, 8, 1, 1, 1, 768), ())</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>((6144, 768, 768, 6144, 768, 1), (0, 0, 19268352, 19268352, 768, 1), ())</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>('', '', 'False')</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>41.664</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.472</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.02604123260350855</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>aten::addmm</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>((400,), (1, 768), (768, 400), (), ())</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>((1,), (19268352, 1), (1, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>('', '', '', '1', '1')</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, false, true, true, false, 7, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;)</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>5.056</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5.056</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.003160149578613172</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>((1, 768, 8), (1, 768, 8), ())</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>((6144, 8, 1), (6144, 1, 768), ())</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>('', '', 'False')</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>3.999</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.999</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.002499493307926043</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>aten::upsample_nearest1d</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>((1, 768, 8), (), ())</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>((6144, 1, 768), (), ())</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>('', '[128]', '')</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>void at::native::(anonymous namespace)::upsample_nearest1d_out_frame&lt;c10::BFloat16, &amp;at::native::nearest_neighbor_compute_source_index&gt;(c10::BFloat16 const*, unsigned long, unsigned long, unsigned long, unsigned long, c10::BFloat16*, float)</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.00144069319199038</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -12428,14 +15165,32 @@
       <c r="N36" t="n">
         <v>3.712242631625875</v>
       </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
+      <c r="O36" t="n">
+        <v>6.144e-06</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.01172065734863281</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.4999186330349878</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="S36" t="n">
+        <v>0.00226974951117672</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3.751008785294355e-05</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.001134690072959298</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.875199184446587e-05</v>
+      </c>
       <c r="W36" t="n">
         <v>5.416035970052083</v>
       </c>
@@ -12454,12 +15209,24 @@
       <c r="AB36" t="n">
         <v>34.46</v>
       </c>
-      <c r="AC36" t="inlineStr"/>
-      <c r="AD36" t="inlineStr"/>
-      <c r="AE36" t="inlineStr"/>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="inlineStr"/>
-      <c r="AH36" t="inlineStr"/>
+      <c r="AC36" t="n">
+        <v>0.002259215510277354</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.002220059095920617</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0.002341823595087458</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0.001129423929629297</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0.001109848908489526</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0.001170721250465203</v>
+      </c>
       <c r="AI36" t="n">
         <v>5.43994140625</v>
       </c>
@@ -12479,9 +15246,13 @@
           <t>[{'name': 'void at::native::reduce_kernel&lt;128, 4, at::native::ReduceOp&lt;c10:...', 'stream': 7, 'mean_duration_us': np.float64(5.42)}]</t>
         </is>
       </c>
-      <c r="AN36" t="inlineStr"/>
+      <c r="AN36" t="inlineStr">
+        <is>
+          <t>{'num_input_elems': 6144, 'num_output_elems': 1, 'dtype_in_out': ('c10::BFloat16', None), 'reduce_type': 'mean'}</t>
+        </is>
+      </c>
       <c r="AO36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP36" t="n">
         <v>0.04102198445609978</v>

--- a/tests/traces/h100/facebook_timesformer-base-finetuned-k400__1016002_perf_report.xlsx
+++ b/tests/traces/h100/facebook_timesformer-base-finetuned-k400__1016002_perf_report.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="CONV_fwd" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="BinaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="UnaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Normalization" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Reduce_fwd" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="kernel_summary" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="short_kernel_histogram" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="short_kernels_summary" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gpu_timeline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary_by_category" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ops_unique_args" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONV_fwd" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BinaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UnaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Normalization" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reduce_fwd" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kernel_summary" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="short_kernel_histogram" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="short_kernels_summary" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>{'elementwise', 'other'}</t>
+          <t>{'other', 'elementwise'}</t>
         </is>
       </c>
       <c r="H5" t="n">

--- a/tests/traces/h100/facebook_timesformer-base-finetuned-k400__1016002_perf_report.xlsx
+++ b/tests/traces/h100/facebook_timesformer-base-finetuned-k400__1016002_perf_report.xlsx
@@ -14,8 +14,8 @@
     <sheet name="unified_perf_summary" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="GEMM" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="CONV_fwd" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="BinaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="UnaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="UnaryElementwise" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="BinaryElementwise" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Normalization" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Reduce_fwd" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="kernel_summary" sheetId="12" state="visible" r:id="rId12"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 13, 'total_duration_us': np.float64(776.062), 'mean_duration_us': np.float64(59.69707692307692), 'median_duration_us': np.float64(59.712), 'std_dev_duration_us': np.float64(0.37602484810253123), 'min_duration_us': np.float64(59.104), 'max_duration_us': np.float64(60.544)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'gpu_op_uid': 47405, 'count': 13, 'total_duration_us': np.float64(776.062), 'mean_duration_us': np.float64(59.69707692307692), 'median_duration_us': np.float64(59.712), 'std_dev_duration_us': np.float64(0.37602484810253123), 'min_duration_us': np.float64(59.104), 'max_duration_us': np.float64(60.544)}]</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 13, 'total_duration_us': np.float64(776.062), 'mean_duration_us': np.float64(59.69707692307692), 'median_duration_us': np.float64(59.712), 'std_dev_duration_us': np.float64(0.37602484810253123), 'min_duration_us': np.float64(59.104), 'max_duration_us': np.float64(60.544)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'gpu_op_uid': 47405, 'count': 13, 'total_duration_us': np.float64(776.062), 'mean_duration_us': np.float64(59.69707692307692), 'median_duration_us': np.float64(59.712), 'std_dev_duration_us': np.float64(0.37602484810253123), 'min_duration_us': np.float64(59.104), 'max_duration_us': np.float64(60.544)}]</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(715.1659999999999), 'mean_duration_us': np.float64(59.59716666666666), 'median_duration_us': np.float64(59.568), 'std_dev_duration_us': np.float64(0.306677037868105), 'min_duration_us': np.float64(59.168), 'max_duration_us': np.float64(60.16)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'gpu_op_uid': 47213, 'count': 12, 'total_duration_us': np.float64(715.1659999999999), 'mean_duration_us': np.float64(59.59716666666666), 'median_duration_us': np.float64(59.568), 'std_dev_duration_us': np.float64(0.306677037868105), 'min_duration_us': np.float64(59.168), 'max_duration_us': np.float64(60.16)}]</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(715.1659999999999), 'mean_duration_us': np.float64(59.59716666666666), 'median_duration_us': np.float64(59.568), 'std_dev_duration_us': np.float64(0.306677037868105), 'min_duration_us': np.float64(59.168), 'max_duration_us': np.float64(60.16)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'gpu_op_uid': 47213, 'count': 12, 'total_duration_us': np.float64(715.1659999999999), 'mean_duration_us': np.float64(59.59716666666666), 'median_duration_us': np.float64(59.568), 'std_dev_duration_us': np.float64(0.306677037868105), 'min_duration_us': np.float64(59.168), 'max_duration_us': np.float64(60.16)}]</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(711.4209999999999), 'mean_duration_us': np.float64(59.285083333333326), 'median_duration_us': np.float64(59.216), 'std_dev_duration_us': np.float64(0.2912291361148854), 'min_duration_us': np.float64(58.815), 'max_duration_us': np.float64(59.808)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'gpu_op_uid': 47313, 'count': 12, 'total_duration_us': np.float64(711.4209999999999), 'mean_duration_us': np.float64(59.285083333333326), 'median_duration_us': np.float64(59.216), 'std_dev_duration_us': np.float64(0.2912291361148854), 'min_duration_us': np.float64(58.815), 'max_duration_us': np.float64(59.808)}]</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(711.4209999999999), 'mean_duration_us': np.float64(59.285083333333326), 'median_duration_us': np.float64(59.216), 'std_dev_duration_us': np.float64(0.2912291361148854), 'min_duration_us': np.float64(58.815), 'max_duration_us': np.float64(59.808)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'gpu_op_uid': 47313, 'count': 12, 'total_duration_us': np.float64(711.4209999999999), 'mean_duration_us': np.float64(59.285083333333326), 'median_duration_us': np.float64(59.216), 'std_dev_duration_us': np.float64(0.2912291361148854), 'min_duration_us': np.float64(58.815), 'max_duration_us': np.float64(59.808)}]</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;128, 4, at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(64.99300000000001), 'mean_duration_us': np.float64(5.416083333333334), 'median_duration_us': np.float64(5.44), 'std_dev_duration_us': np.float64(0.08484540680293502), 'min_duration_us': np.float64(5.248), 'max_duration_us': np.float64(5.536)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;128, 4, at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)', 'stream': 7, 'gpu_op_uid': 47385, 'count': 12, 'total_duration_us': np.float64(64.99300000000001), 'mean_duration_us': np.float64(5.416083333333334), 'median_duration_us': np.float64(5.44), 'std_dev_duration_us': np.float64(0.08484540680293502), 'min_duration_us': np.float64(5.248), 'max_duration_us': np.float64(5.536)}]</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::cunn_SoftMaxForward&lt;8, c10::BFloat16, float, c10::BFloat16, at::native::(anonymous namespace)::SoftMaxForwardEpilogue&gt;(c10::BFloat16*, c10::BFloat16 const*, int)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(68688.625), 'mean_duration_us': np.float64(5724.052083333333), 'median_duration_us': np.float64(5706.610000000001), 'std_dev_duration_us': np.float64(26.445577605900787), 'min_duration_us': np.float64(5701.537), 'max_duration_us': np.float64(5767.809)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::cunn_SoftMaxForward&lt;8, c10::BFloat16, float, c10::BFloat16, at::native::(anonymous namespace)::SoftMaxForwardEpilogue&gt;(c10::BFloat16*, c10::BFloat16 const*, int)', 'stream': 7, 'gpu_op_uid': 47351, 'count': 12, 'total_duration_us': np.float64(68688.625), 'mean_duration_us': np.float64(5724.052083333333), 'median_duration_us': np.float64(5706.610000000001), 'std_dev_duration_us': np.float64(26.445577605900787), 'min_duration_us': np.float64(5701.537), 'max_duration_us': np.float64(5767.809)}]</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1&gt;(cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1::Params)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(22819.528), 'mean_duration_us': np.float64(1901.6273333333331), 'median_duration_us': np.float64(1897.1419999999998), 'std_dev_duration_us': np.float64(12.13592587687027), 'min_duration_us': np.float64(1889.59), 'max_duration_us': np.float64(1919.478)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1&gt;(cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1::Params)', 'stream': 7, 'gpu_op_uid': 47343, 'count': 12, 'total_duration_us': np.float64(22819.528), 'mean_duration_us': np.float64(1901.6273333333331), 'median_duration_us': np.float64(1897.1419999999998), 'std_dev_duration_us': np.float64(12.13592587687027), 'min_duration_us': np.float64(1889.59), 'max_duration_us': np.float64(1919.478)}]</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -9562,7 +9562,7 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1&gt;(cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1::Params)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(20388.114), 'mean_duration_us': np.float64(1699.0095000000001), 'median_duration_us': np.float64(1693.687), 'std_dev_duration_us': np.float64(11.565890623582206), 'min_duration_us': np.float64(1682.295), 'max_duration_us': np.float64(1718.295)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1&gt;(cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1::Params)', 'stream': 7, 'gpu_op_uid': 47361, 'count': 12, 'total_duration_us': np.float64(20388.114), 'mean_duration_us': np.float64(1699.0095000000001), 'median_duration_us': np.float64(1693.687), 'std_dev_duration_us': np.float64(11.565890623582206), 'min_duration_us': np.float64(1682.295), 'max_duration_us': np.float64(1718.295)}]</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -9719,7 +9719,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(15495.243999999999), 'mean_duration_us': np.float64(1291.2703333333332), 'median_duration_us': np.float64(1291.129), 'std_dev_duration_us': np.float64(0.8817396945181291), 'min_duration_us': np.float64(1289.657), 'max_duration_us': np.float64(1292.505)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'gpu_op_uid': 47347, 'count': 12, 'total_duration_us': np.float64(15495.243999999999), 'mean_duration_us': np.float64(1291.2703333333332), 'median_duration_us': np.float64(1291.129), 'std_dev_duration_us': np.float64(0.8817396945181291), 'min_duration_us': np.float64(1289.657), 'max_duration_us': np.float64(1292.505)}]</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3461.358), 'mean_duration_us': np.float64(3461.358), 'median_duration_us': np.float64(3461.358), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3461.358), 'max_duration_us': np.float64(3461.358)}]</t>
+          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'gpu_op_uid': 47137, 'count': 1, 'total_duration_us': np.float64(3461.358), 'mean_duration_us': np.float64(3461.358), 'median_duration_us': np.float64(3461.358), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3461.358), 'max_duration_us': np.float64(3461.358)}]</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -10025,7 +10025,7 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(10.270000000000001), 'mean_duration_us': np.float64(0.8558333333333334), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.10186333436958013), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.087)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(1967.4789999999998), 'mean_duration_us': np.float64(163.95658333333333), 'median_duration_us': np.float64(164.04700000000003), 'std_dev_duration_us': np.float64(0.7758030740608224), 'min_duration_us': np.float64(162.815), 'max_duration_us': np.float64(165.887)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'gpu_op_uid': 47411, 'count': 12, 'total_duration_us': np.float64(10.270000000000001), 'mean_duration_us': np.float64(0.8558333333333334), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.10186333436958013), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.087)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'gpu_op_uid': 47421, 'count': 12, 'total_duration_us': np.float64(1967.4789999999998), 'mean_duration_us': np.float64(163.95658333333333), 'median_duration_us': np.float64(164.04700000000003), 'std_dev_duration_us': np.float64(0.7758030740608224), 'min_duration_us': np.float64(162.815), 'max_duration_us': np.float64(165.887)}]</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(13.661999999999999), 'mean_duration_us': np.float64(1.1384999999999998), 'median_duration_us': np.float64(1.168), 'std_dev_duration_us': np.float64(0.18668846598901961), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.376)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(1890.9), 'mean_duration_us': np.float64(157.57500000000002), 'median_duration_us': np.float64(158.031), 'std_dev_duration_us': np.float64(2.2915636582909897), 'min_duration_us': np.float64(151.199), 'max_duration_us': np.float64(160.415)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'gpu_op_uid': 47431, 'count': 12, 'total_duration_us': np.float64(13.661999999999999), 'mean_duration_us': np.float64(1.1384999999999998), 'median_duration_us': np.float64(1.168), 'std_dev_duration_us': np.float64(0.18668846598901961), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.376)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'gpu_op_uid': 47441, 'count': 12, 'total_duration_us': np.float64(1890.9), 'mean_duration_us': np.float64(157.57500000000002), 'median_duration_us': np.float64(158.031), 'std_dev_duration_us': np.float64(2.2915636582909897), 'min_duration_us': np.float64(151.199), 'max_duration_us': np.float64(160.415)}]</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(1846.007), 'mean_duration_us': np.float64(153.83391666666668), 'median_duration_us': np.float64(153.8075), 'std_dev_duration_us': np.float64(0.17379991289475016), 'min_duration_us': np.float64(153.6), 'max_duration_us': np.float64(154.079)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 47337, 'count': 12, 'total_duration_us': np.float64(1846.007), 'mean_duration_us': np.float64(153.83391666666668), 'median_duration_us': np.float64(153.8075), 'std_dev_duration_us': np.float64(0.17379991289475016), 'min_duration_us': np.float64(153.6), 'max_duration_us': np.float64(154.079)}]</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(1534.2), 'mean_duration_us': np.float64(127.85000000000001), 'median_duration_us': np.float64(127.7915), 'std_dev_duration_us': np.float64(0.47875602694204833), 'min_duration_us': np.float64(127.103), 'max_duration_us': np.float64(128.703)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::GeluCUDAKernelImpl(at::TensorIteratorBase&amp;, at::native::GeluType)::{lambda()#2}::operator()() const::{lambda()#4}::operator()() const::{lambda(c10::BFloat16)#1}, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'gpu_op_uid': 47425, 'count': 12, 'total_duration_us': np.float64(1534.2), 'mean_duration_us': np.float64(127.85000000000001), 'median_duration_us': np.float64(127.7915), 'std_dev_duration_us': np.float64(0.47875602694204833), 'min_duration_us': np.float64(127.103), 'max_duration_us': np.float64(128.703)}]</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(10.656000000000002), 'mean_duration_us': np.float64(0.8880000000000002), 'median_duration_us': np.float64(0.8640000000000001), 'std_dev_duration_us': np.float64(0.10939835464941874), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.12)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(1501.144), 'mean_duration_us': np.float64(125.09533333333333), 'median_duration_us': np.float64(124.703), 'std_dev_duration_us': np.float64(1.0343101834341377), 'min_duration_us': np.float64(123.967), 'max_duration_us': np.float64(127.007)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'gpu_op_uid': 47319, 'count': 12, 'total_duration_us': np.float64(10.656000000000002), 'mean_duration_us': np.float64(0.8880000000000002), 'median_duration_us': np.float64(0.8640000000000001), 'std_dev_duration_us': np.float64(0.10939835464941874), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.12)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'gpu_op_uid': 47329, 'count': 12, 'total_duration_us': np.float64(1501.144), 'mean_duration_us': np.float64(125.09533333333333), 'median_duration_us': np.float64(124.703), 'std_dev_duration_us': np.float64(1.0343101834341377), 'min_duration_us': np.float64(123.967), 'max_duration_us': np.float64(127.007)}]</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -10776,7 +10776,7 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(10.401000000000003), 'mean_duration_us': np.float64(0.8667500000000002), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.11950113318849044), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.089)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(1468.15), 'mean_duration_us': np.float64(122.34583333333335), 'median_duration_us': np.float64(122.079), 'std_dev_duration_us': np.float64(0.8646479855345122), 'min_duration_us': np.float64(121.151), 'max_duration_us': np.float64(124.479)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'gpu_op_uid': 47219, 'count': 12, 'total_duration_us': np.float64(10.401000000000003), 'mean_duration_us': np.float64(0.8667500000000002), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.11950113318849044), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.089)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'gpu_op_uid': 47229, 'count': 12, 'total_duration_us': np.float64(1468.15), 'mean_duration_us': np.float64(122.34583333333335), 'median_duration_us': np.float64(122.079), 'std_dev_duration_us': np.float64(0.8646479855345122), 'min_duration_us': np.float64(121.151), 'max_duration_us': np.float64(124.479)}]</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -10933,7 +10933,7 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(1418.552), 'mean_duration_us': np.float64(59.10633333333333), 'median_duration_us': np.float64(59.167500000000004), 'std_dev_duration_us': np.float64(0.7604596563190504), 'min_duration_us': np.float64(57.92), 'max_duration_us': np.float64(60.223)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 47333, 'count': 24, 'total_duration_us': np.float64(1418.552), 'mean_duration_us': np.float64(59.10633333333333), 'median_duration_us': np.float64(59.167500000000004), 'std_dev_duration_us': np.float64(0.7604596563190504), 'min_duration_us': np.float64(57.92), 'max_duration_us': np.float64(60.223)}]</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -11090,7 +11090,7 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(1400.504), 'mean_duration_us': np.float64(58.35433333333333), 'median_duration_us': np.float64(58.4955), 'std_dev_duration_us': np.float64(1.4517576320523424), 'min_duration_us': np.float64(56.575), 'max_duration_us': np.float64(60.16)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 47233, 'count': 24, 'total_duration_us': np.float64(1400.504), 'mean_duration_us': np.float64(58.35433333333333), 'median_duration_us': np.float64(58.4955), 'std_dev_duration_us': np.float64(1.4517576320523424), 'min_duration_us': np.float64(56.575), 'max_duration_us': np.float64(60.16)}]</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -11247,7 +11247,7 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_16x16_32x1_nn_align8&gt;(cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_16x16_32x1_nn_align8::Params)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(1300.504), 'mean_duration_us': np.float64(108.37533333333333), 'median_duration_us': np.float64(107.8715), 'std_dev_duration_us': np.float64(0.8493324175819239), 'min_duration_us': np.float64(107.583), 'max_duration_us': np.float64(109.599)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_16x16_32x1_nn_align8&gt;(cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_16x16_32x1_nn_align8::Params)', 'stream': 7, 'gpu_op_uid': 47261, 'count': 12, 'total_duration_us': np.float64(1300.504), 'mean_duration_us': np.float64(108.37533333333333), 'median_duration_us': np.float64(107.8715), 'std_dev_duration_us': np.float64(0.8493324175819239), 'min_duration_us': np.float64(107.583), 'max_duration_us': np.float64(109.599)}]</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -11396,7 +11396,7 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(32.448), 'mean_duration_us': np.float64(32.448), 'median_duration_us': np.float64(32.448), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(32.448), 'max_duration_us': np.float64(32.448)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(281.343), 'mean_duration_us': np.float64(281.343), 'median_duration_us': np.float64(281.343), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(281.343), 'max_duration_us': np.float64(281.343)}, {'name': 'Memset (Device)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.336), 'mean_duration_us': np.float64(2.336), 'median_duration_us': np.float64(2.336), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.336), 'max_duration_us': np.float64(2.336)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(10.336), 'mean_duration_us': np.float64(10.336), 'median_duration_us': np.float64(10.336), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(10.336), 'max_duration_us': np.float64(10.336)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8&gt;(cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8::Params)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(863.099), 'mean_duration_us': np.float64(863.099), 'median_duration_us': np.float64(863.099), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(863.099), 'max_duration_us': np.float64(863.099)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(43.488), 'mean_duration_us': np.float64(43.488), 'median_duration_us': np.float64(43.488), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(43.488), 'max_duration_us': np.float64(43.488)}, {'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(64.864), 'mean_duration_us': np.float64(64.864), 'median_duration_us': np.float64(64.864), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(64.864), 'max_duration_us': np.float64(64.864)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'gpu_op_uid': 47151, 'count': 1, 'total_duration_us': np.float64(32.448), 'mean_duration_us': np.float64(32.448), 'median_duration_us': np.float64(32.448), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(32.448), 'max_duration_us': np.float64(32.448)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'gpu_op_uid': 47155, 'count': 1, 'total_duration_us': np.float64(281.343), 'mean_duration_us': np.float64(281.343), 'median_duration_us': np.float64(281.343), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(281.343), 'max_duration_us': np.float64(281.343)}, {'name': 'Memset (Device)', 'stream': 7, 'gpu_op_uid': 47159, 'count': 1, 'total_duration_us': np.float64(2.336), 'mean_duration_us': np.float64(2.336), 'median_duration_us': np.float64(2.336), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.336), 'max_duration_us': np.float64(2.336)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'gpu_op_uid': 47163, 'count': 1, 'total_duration_us': np.float64(10.336), 'mean_duration_us': np.float64(10.336), 'median_duration_us': np.float64(10.336), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(10.336), 'max_duration_us': np.float64(10.336)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8&gt;(cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8::Params)', 'stream': 7, 'gpu_op_uid': 47171, 'count': 1, 'total_duration_us': np.float64(863.099), 'mean_duration_us': np.float64(863.099), 'median_duration_us': np.float64(863.099), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(863.099), 'max_duration_us': np.float64(863.099)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'gpu_op_uid': 47177, 'count': 1, 'total_duration_us': np.float64(43.488), 'mean_duration_us': np.float64(43.488), 'median_duration_us': np.float64(43.488), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(43.488), 'max_duration_us': np.float64(43.488)}, {'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 47181, 'count': 1, 'total_duration_us': np.float64(64.864), 'mean_duration_us': np.float64(64.864), 'median_duration_us': np.float64(64.864), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(64.864), 'max_duration_us': np.float64(64.864)}]</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -11523,7 +11523,7 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(1140.8580000000002), 'mean_duration_us': np.float64(95.07150000000001), 'median_duration_us': np.float64(95.007), 'std_dev_duration_us': np.float64(0.5674224616632664), 'min_duration_us': np.float64(93.823), 'max_duration_us': np.float64(96.0)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 7, 'gpu_op_uid': 47309, 'count': 12, 'total_duration_us': np.float64(1140.8580000000002), 'mean_duration_us': np.float64(95.07150000000001), 'median_duration_us': np.float64(95.007), 'std_dev_duration_us': np.float64(0.5674224616632664), 'min_duration_us': np.float64(93.823), 'max_duration_us': np.float64(96.0)}]</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(23.326999999999998), 'mean_duration_us': np.float64(0.9719583333333333), 'median_duration_us': np.float64(0.96), 'std_dev_duration_us': np.float64(0.1973181608398533), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.439)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(1101.214), 'mean_duration_us': np.float64(45.883916666666664), 'median_duration_us': np.float64(45.936), 'std_dev_duration_us': np.float64(0.6211491310913646), 'min_duration_us': np.float64(44.992), 'max_duration_us': np.float64(47.008)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'gpu_op_uid': 47271, 'count': 24, 'total_duration_us': np.float64(23.326999999999998), 'mean_duration_us': np.float64(0.9719583333333333), 'median_duration_us': np.float64(0.96), 'std_dev_duration_us': np.float64(0.1973181608398533), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.439)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'gpu_op_uid': 47281, 'count': 24, 'total_duration_us': np.float64(1101.214), 'mean_duration_us': np.float64(45.883916666666664), 'median_duration_us': np.float64(45.936), 'std_dev_duration_us': np.float64(0.6211491310913646), 'min_duration_us': np.float64(44.992), 'max_duration_us': np.float64(47.008)}]</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(891.774), 'mean_duration_us': np.float64(37.15725), 'median_duration_us': np.float64(37.471999999999994), 'std_dev_duration_us': np.float64(1.5359198723132224), 'min_duration_us': np.float64(35.04), 'max_duration_us': np.float64(39.296)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'gpu_op_uid': 47401, 'count': 24, 'total_duration_us': np.float64(891.774), 'mean_duration_us': np.float64(37.15725), 'median_duration_us': np.float64(37.471999999999994), 'std_dev_duration_us': np.float64(1.5359198723132224), 'min_duration_us': np.float64(35.04), 'max_duration_us': np.float64(39.296)}]</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -11960,7 +11960,7 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy_contig&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 128, 1&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 128, 1&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(857.179), 'mean_duration_us': np.float64(71.43158333333334), 'median_duration_us': np.float64(71.52), 'std_dev_duration_us': np.float64(0.40444395127411975), 'min_duration_us': np.float64(70.559), 'max_duration_us': np.float64(72.223)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy_contig&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 128, 1&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 128, 1&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 7, 'gpu_op_uid': 47397, 'count': 12, 'total_duration_us': np.float64(857.179), 'mean_duration_us': np.float64(71.43158333333334), 'median_duration_us': np.float64(71.52), 'std_dev_duration_us': np.float64(0.40444395127411975), 'min_duration_us': np.float64(70.559), 'max_duration_us': np.float64(72.223)}]</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy_contig&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 128, 1&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 128, 1&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(852.026), 'mean_duration_us': np.float64(71.00216666666667), 'median_duration_us': np.float64(70.9915), 'std_dev_duration_us': np.float64(0.4709237081405958), 'min_duration_us': np.float64(69.983), 'max_duration_us': np.float64(71.584)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy_contig&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 128, 1&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 128, 1&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 7, 'gpu_op_uid': 47393, 'count': 12, 'total_duration_us': np.float64(852.026), 'mean_duration_us': np.float64(71.00216666666667), 'median_duration_us': np.float64(70.9915), 'std_dev_duration_us': np.float64(0.4709237081405958), 'min_duration_us': np.float64(69.983), 'max_duration_us': np.float64(71.584)}]</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -12236,7 +12236,7 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 13, 'total_duration_us': np.float64(776.062), 'mean_duration_us': np.float64(59.69707692307692), 'median_duration_us': np.float64(59.712), 'std_dev_duration_us': np.float64(0.37602484810253123), 'min_duration_us': np.float64(59.104), 'max_duration_us': np.float64(60.544)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'gpu_op_uid': 47405, 'count': 13, 'total_duration_us': np.float64(776.062), 'mean_duration_us': np.float64(59.69707692307692), 'median_duration_us': np.float64(59.712), 'std_dev_duration_us': np.float64(0.37602484810253123), 'min_duration_us': np.float64(59.104), 'max_duration_us': np.float64(60.544)}]</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(715.1659999999999), 'mean_duration_us': np.float64(59.59716666666666), 'median_duration_us': np.float64(59.568), 'std_dev_duration_us': np.float64(0.306677037868105), 'min_duration_us': np.float64(59.168), 'max_duration_us': np.float64(60.16)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'gpu_op_uid': 47213, 'count': 12, 'total_duration_us': np.float64(715.1659999999999), 'mean_duration_us': np.float64(59.59716666666666), 'median_duration_us': np.float64(59.568), 'std_dev_duration_us': np.float64(0.306677037868105), 'min_duration_us': np.float64(59.168), 'max_duration_us': np.float64(60.16)}]</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -12550,7 +12550,7 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(711.4209999999999), 'mean_duration_us': np.float64(59.285083333333326), 'median_duration_us': np.float64(59.216), 'std_dev_duration_us': np.float64(0.2912291361148854), 'min_duration_us': np.float64(58.815), 'max_duration_us': np.float64(59.808)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::vectorized_layer_norm_kernel&lt;c10::BFloat16, float&gt;(int, float, c10::BFloat16 const*, c10::BFloat16 const*, c10::BFloat16 const*, float*, float*, c10::BFloat16*)', 'stream': 7, 'gpu_op_uid': 47313, 'count': 12, 'total_duration_us': np.float64(711.4209999999999), 'mean_duration_us': np.float64(59.285083333333326), 'median_duration_us': np.float64(59.216), 'std_dev_duration_us': np.float64(0.2912291361148854), 'min_duration_us': np.float64(58.815), 'max_duration_us': np.float64(59.808)}]</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
@@ -12707,7 +12707,7 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(686.844), 'mean_duration_us': np.float64(57.237), 'median_duration_us': np.float64(57.2315), 'std_dev_duration_us': np.float64(0.2646696053573195), 'min_duration_us': np.float64(56.895), 'max_duration_us': np.float64(57.696)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 47265, 'count': 12, 'total_duration_us': np.float64(686.844), 'mean_duration_us': np.float64(57.237), 'median_duration_us': np.float64(57.2315), 'std_dev_duration_us': np.float64(0.2646696053573195), 'min_duration_us': np.float64(56.895), 'max_duration_us': np.float64(57.696)}]</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
@@ -12864,7 +12864,7 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(678.1399999999999), 'mean_duration_us': np.float64(56.511666666666656), 'median_duration_us': np.float64(56.4795), 'std_dev_duration_us': np.float64(0.17831869098766825), 'min_duration_us': np.float64(56.223), 'max_duration_us': np.float64(56.928)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 47365, 'count': 12, 'total_duration_us': np.float64(678.1399999999999), 'mean_duration_us': np.float64(56.511666666666656), 'median_duration_us': np.float64(56.4795), 'std_dev_duration_us': np.float64(0.17831869098766825), 'min_duration_us': np.float64(56.223), 'max_duration_us': np.float64(56.928)}]</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(637.9490000000001), 'mean_duration_us': np.float64(53.16241666666667), 'median_duration_us': np.float64(53.184), 'std_dev_duration_us': np.float64(0.31582021740576044), 'min_duration_us': np.float64(52.64), 'max_duration_us': np.float64(53.664)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 47389, 'count': 12, 'total_duration_us': np.float64(637.9490000000001), 'mean_duration_us': np.float64(53.16241666666667), 'median_duration_us': np.float64(53.184), 'std_dev_duration_us': np.float64(0.31582021740576044), 'min_duration_us': np.float64(52.64), 'max_duration_us': np.float64(53.664)}]</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(612.698), 'mean_duration_us': np.float64(51.058166666666665), 'median_duration_us': np.float64(51.055499999999995), 'std_dev_duration_us': np.float64(0.36143575577902604), 'min_duration_us': np.float64(50.495), 'max_duration_us': np.float64(51.616)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 47237, 'count': 12, 'total_duration_us': np.float64(612.698), 'mean_duration_us': np.float64(51.058166666666665), 'median_duration_us': np.float64(51.055499999999995), 'std_dev_duration_us': np.float64(0.36143575577902604), 'min_duration_us': np.float64(50.495), 'max_duration_us': np.float64(51.616)}]</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
@@ -13335,7 +13335,7 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(10.337000000000003), 'mean_duration_us': np.float64(0.8614166666666669), 'median_duration_us': np.float64(0.7995000000000001), 'std_dev_duration_us': np.float64(0.12347837754935968), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.152)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(557.277), 'mean_duration_us': np.float64(46.439750000000004), 'median_duration_us': np.float64(46.432), 'std_dev_duration_us': np.float64(0.4246459554734984), 'min_duration_us': np.float64(45.951), 'max_duration_us': np.float64(47.295)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'gpu_op_uid': 47371, 'count': 12, 'total_duration_us': np.float64(10.337000000000003), 'mean_duration_us': np.float64(0.8614166666666669), 'median_duration_us': np.float64(0.7995000000000001), 'std_dev_duration_us': np.float64(0.12347837754935968), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.152)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'gpu_op_uid': 47381, 'count': 12, 'total_duration_us': np.float64(557.277), 'mean_duration_us': np.float64(46.439750000000004), 'median_duration_us': np.float64(46.432), 'std_dev_duration_us': np.float64(0.4246459554734984), 'min_duration_us': np.float64(45.951), 'max_duration_us': np.float64(47.295)}]</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
@@ -13492,7 +13492,7 @@
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_16x16_64x1_nn_align8&gt;(cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_16x16_64x1_nn_align8::Params)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(490.207), 'mean_duration_us': np.float64(40.85058333333333), 'median_duration_us': np.float64(40.7355), 'std_dev_duration_us': np.float64(0.4567669825949428), 'min_duration_us': np.float64(40.288), 'max_duration_us': np.float64(41.632)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_16x16_64x1_nn_align8&gt;(cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_16x16_64x1_nn_align8::Params)', 'stream': 7, 'gpu_op_uid': 47243, 'count': 12, 'total_duration_us': np.float64(490.207), 'mean_duration_us': np.float64(40.85058333333333), 'median_duration_us': np.float64(40.7355), 'std_dev_duration_us': np.float64(0.4567669825949428), 'min_duration_us': np.float64(40.288), 'max_duration_us': np.float64(41.632)}]</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(468.6050000000001), 'mean_duration_us': np.float64(39.05041666666667), 'median_duration_us': np.float64(38.976), 'std_dev_duration_us': np.float64(0.46841407222195597), 'min_duration_us': np.float64(38.432), 'max_duration_us': np.float64(39.936)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'gpu_op_uid': 47301, 'count': 12, 'total_duration_us': np.float64(468.6050000000001), 'mean_duration_us': np.float64(39.05041666666667), 'median_duration_us': np.float64(38.976), 'std_dev_duration_us': np.float64(0.46841407222195597), 'min_duration_us': np.float64(38.432), 'max_duration_us': np.float64(39.936)}]</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -13772,7 +13772,7 @@
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(161.311), 'mean_duration_us': np.float64(161.311), 'median_duration_us': np.float64(161.311), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(161.311), 'max_duration_us': np.float64(161.311)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 64, 64&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 64, 64&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 7, 'gpu_op_uid': 47185, 'count': 1, 'total_duration_us': np.float64(161.311), 'mean_duration_us': np.float64(161.311), 'median_duration_us': np.float64(161.311), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(161.311), 'max_duration_us': np.float64(161.311)}]</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -13895,7 +13895,7 @@
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>[{'name': 'void (anonymous namespace)::softmax_warp_forward&lt;c10::BFloat16, c10::BFloat16, float, 3, false, false&gt;(c10::BFloat16*, c10::BFloat16 const*, int, int, int, bool const*, int, bool)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(92.672), 'mean_duration_us': np.float64(7.722666666666666), 'median_duration_us': np.float64(7.712), 'std_dev_duration_us': np.float64(0.04617057745168701), 'min_duration_us': np.float64(7.679), 'max_duration_us': np.float64(7.841)}]</t>
+          <t>[{'name': 'void (anonymous namespace)::softmax_warp_forward&lt;c10::BFloat16, c10::BFloat16, float, 3, false, false&gt;(c10::BFloat16*, c10::BFloat16 const*, int, int, int, bool const*, int, bool)', 'stream': 7, 'gpu_op_uid': 47251, 'count': 12, 'total_duration_us': np.float64(92.672), 'mean_duration_us': np.float64(7.722666666666666), 'median_duration_us': np.float64(7.712), 'std_dev_duration_us': np.float64(0.04617057745168701), 'min_duration_us': np.float64(7.679), 'max_duration_us': np.float64(7.841)}]</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -14040,7 +14040,7 @@
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(86.08), 'mean_duration_us': np.float64(86.08), 'median_duration_us': np.float64(86.08), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(86.08), 'max_duration_us': np.float64(86.08)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 47201, 'count': 1, 'total_duration_us': np.float64(86.08), 'mean_duration_us': np.float64(86.08), 'median_duration_us': np.float64(86.08), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(86.08), 'max_duration_us': np.float64(86.08)}]</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy_contig&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 128, 1&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 128, 1&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(71.743), 'mean_duration_us': np.float64(71.743), 'median_duration_us': np.float64(71.743), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(71.743), 'max_duration_us': np.float64(71.743)}]</t>
+          <t>[{'name': 'void at::native::(anonymous namespace)::CatArrayBatchedCopy_contig&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 3, 128, 1&gt;(at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;*, at::native::(anonymous namespace)::CatArrInputTensorMetadata&lt;at::native::(anonymous namespace)::OpaqueType&lt;2u&gt;, unsigned int, 128, 1&gt;, at::native::(anonymous namespace)::TensorSizeStride&lt;unsigned int, 4u&gt;, int, unsigned int)', 'stream': 7, 'gpu_op_uid': 47209, 'count': 1, 'total_duration_us': np.float64(71.743), 'mean_duration_us': np.float64(71.743), 'median_duration_us': np.float64(71.743), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(71.743), 'max_duration_us': np.float64(71.743)}]</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
@@ -14316,7 +14316,7 @@
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::reduce_kernel&lt;128, 4, at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(64.99300000000001), 'mean_duration_us': np.float64(5.416083333333334), 'median_duration_us': np.float64(5.44), 'std_dev_duration_us': np.float64(0.08484540680293502), 'min_duration_us': np.float64(5.248), 'max_duration_us': np.float64(5.536)}]</t>
+          <t>[{'name': 'void at::native::reduce_kernel&lt;128, 4, at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt; &gt;(at::native::ReduceOp&lt;c10::BFloat16, at::native::MeanOps&lt;c10::BFloat16, float, float, c10::BFloat16&gt;, unsigned int, c10::BFloat16, 4&gt;)', 'stream': 7, 'gpu_op_uid': 47385, 'count': 12, 'total_duration_us': np.float64(64.99300000000001), 'mean_duration_us': np.float64(5.416083333333334), 'median_duration_us': np.float64(5.44), 'std_dev_duration_us': np.float64(0.08484540680293502), 'min_duration_us': np.float64(5.248), 'max_duration_us': np.float64(5.536)}]</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -14473,7 +14473,7 @@
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(60.544), 'mean_duration_us': np.float64(5.045333333333333), 'median_duration_us': np.float64(4.96), 'std_dev_duration_us': np.float64(0.24591236017916807), 'min_duration_us': np.float64(4.896), 'max_duration_us': np.float64(5.824)}]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'gpu_op_uid': 47247, 'count': 12, 'total_duration_us': np.float64(60.544), 'mean_duration_us': np.float64(5.045333333333333), 'median_duration_us': np.float64(4.96), 'std_dev_duration_us': np.float64(0.24591236017916807), 'min_duration_us': np.float64(4.896), 'max_duration_us': np.float64(5.824)}]</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
@@ -14622,7 +14622,7 @@
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(53.983), 'mean_duration_us': np.float64(53.983), 'median_duration_us': np.float64(53.983), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(53.983), 'max_duration_us': np.float64(53.983)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 47189, 'count': 1, 'total_duration_us': np.float64(53.983), 'mean_duration_us': np.float64(53.983), 'median_duration_us': np.float64(53.983), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(53.983), 'max_duration_us': np.float64(53.983)}]</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
@@ -14771,7 +14771,7 @@
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(51.744), 'mean_duration_us': np.float64(51.744), 'median_duration_us': np.float64(51.744), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(51.744), 'max_duration_us': np.float64(51.744)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 47205, 'count': 1, 'total_duration_us': np.float64(51.744), 'mean_duration_us': np.float64(51.744), 'median_duration_us': np.float64(51.744), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(51.744), 'max_duration_us': np.float64(51.744)}]</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
@@ -14928,7 +14928,7 @@
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(41.66400000000001), 'mean_duration_us': np.float64(3.472000000000001), 'median_duration_us': np.float64(3.52), 'std_dev_duration_us': np.float64(0.17008233300375442), 'min_duration_us': np.float64(2.944), 'max_duration_us': np.float64(3.648)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 47305, 'count': 12, 'total_duration_us': np.float64(41.66400000000001), 'mean_duration_us': np.float64(3.472000000000001), 'median_duration_us': np.float64(3.52), 'std_dev_duration_us': np.float64(0.17008233300375442), 'min_duration_us': np.float64(2.944), 'max_duration_us': np.float64(3.648)}]</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.999), 'mean_duration_us': np.float64(3.999), 'median_duration_us': np.float64(3.999), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.999), 'max_duration_us': np.float64(3.999)}, {'name': 'void at::native::(anonymous namespace)::upsample_nearest1d_out_frame&lt;c10::BFloat16, &amp;at::native::nearest_neighbor_compute_source_index&gt;(c10::BFloat16 const*, unsigned long, unsigned long, unsigned long, unsigned long, c10::BFloat16*, float)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.305), 'mean_duration_us': np.float64(2.305), 'median_duration_us': np.float64(2.305), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.305), 'max_duration_us': np.float64(2.305)}]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 47193, 'count': 1, 'total_duration_us': np.float64(3.999), 'mean_duration_us': np.float64(3.999), 'median_duration_us': np.float64(3.999), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.999), 'max_duration_us': np.float64(3.999)}, {'name': 'void at::native::(anonymous namespace)::upsample_nearest1d_out_frame&lt;c10::BFloat16, &amp;at::native::nearest_neighbor_compute_source_index&gt;(c10::BFloat16 const*, unsigned long, unsigned long, unsigned long, unsigned long, c10::BFloat16*, float)', 'stream': 7, 'gpu_op_uid': 47197, 'count': 1, 'total_duration_us': np.float64(2.305), 'mean_duration_us': np.float64(2.305), 'median_duration_us': np.float64(2.305), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.305), 'max_duration_us': np.float64(2.305)}]</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
@@ -15196,7 +15196,7 @@
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>[{'name': 'std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, false, true, true, false, 7, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(5.056), 'mean_duration_us': np.float64(5.056), 'median_duration_us': np.float64(5.056), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(5.056), 'max_duration_us': np.float64(5.056)}]</t>
+          <t>[{'name': 'std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, false, true, true, false, 7, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;)', 'stream': 7, 'gpu_op_uid': 50049, 'count': 1, 'total_duration_us': np.float64(5.056), 'mean_duration_us': np.float64(5.056), 'median_duration_us': np.float64(5.056), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(5.056), 'max_duration_us': np.float64(5.056)}]</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
@@ -15345,7 +15345,7 @@
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.784), 'mean_duration_us': np.float64(2.784), 'median_duration_us': np.float64(2.784), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.784), 'max_duration_us': np.float64(2.784)}]</t>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'gpu_op_uid': 50053, 'count': 1, 'total_duration_us': np.float64(2.784), 'mean_duration_us': np.float64(2.784), 'median_duration_us': np.float64(2.784), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.784), 'max_duration_us': np.float64(2.784)}]</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
@@ -15691,7 +15691,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1&gt;(cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1::Params)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(22819.528), 'mean_duration_us': np.float64(1901.6273333333331), 'median_duration_us': np.float64(1897.1419999999998), 'std_dev_duration_us': np.float64(12.13592587687027), 'min_duration_us': np.float64(1889.59), 'max_duration_us': np.float64(1919.478)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1&gt;(cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1::Params)', 'stream': 7, 'gpu_op_uid': 47343, 'count': 12, 'total_duration_us': np.float64(22819.528), 'mean_duration_us': np.float64(1901.6273333333331), 'median_duration_us': np.float64(1897.1419999999998), 'std_dev_duration_us': np.float64(12.13592587687027), 'min_duration_us': np.float64(1889.59), 'max_duration_us': np.float64(1919.478)}]</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -15851,7 +15851,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1&gt;(cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1::Params)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(20388.114), 'mean_duration_us': np.float64(1699.0095000000001), 'median_duration_us': np.float64(1693.687), 'std_dev_duration_us': np.float64(11.565890623582206), 'min_duration_us': np.float64(1682.295), 'max_duration_us': np.float64(1718.295)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1&gt;(cutlass_75_tensorop_bf16_s1688gemm_bf16_128x128_nn_align1::Params)', 'stream': 7, 'gpu_op_uid': 47361, 'count': 12, 'total_duration_us': np.float64(20388.114), 'mean_duration_us': np.float64(1699.0095000000001), 'median_duration_us': np.float64(1693.687), 'std_dev_duration_us': np.float64(11.565890623582206), 'min_duration_us': np.float64(1682.295), 'max_duration_us': np.float64(1718.295)}]</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -16011,7 +16011,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(10.270000000000001), 'mean_duration_us': np.float64(0.8558333333333334), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.10186333436958013), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.087)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(1967.4789999999998), 'mean_duration_us': np.float64(163.95658333333333), 'median_duration_us': np.float64(164.04700000000003), 'std_dev_duration_us': np.float64(0.7758030740608224), 'min_duration_us': np.float64(162.815), 'max_duration_us': np.float64(165.887)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'gpu_op_uid': 47411, 'count': 12, 'total_duration_us': np.float64(10.270000000000001), 'mean_duration_us': np.float64(0.8558333333333334), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.10186333436958013), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.087)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'gpu_op_uid': 47421, 'count': 12, 'total_duration_us': np.float64(1967.4789999999998), 'mean_duration_us': np.float64(163.95658333333333), 'median_duration_us': np.float64(164.04700000000003), 'std_dev_duration_us': np.float64(0.7758030740608224), 'min_duration_us': np.float64(162.815), 'max_duration_us': np.float64(165.887)}]</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -16171,7 +16171,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(13.661999999999999), 'mean_duration_us': np.float64(1.1384999999999998), 'median_duration_us': np.float64(1.168), 'std_dev_duration_us': np.float64(0.18668846598901961), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.376)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(1890.9), 'mean_duration_us': np.float64(157.57500000000002), 'median_duration_us': np.float64(158.031), 'std_dev_duration_us': np.float64(2.2915636582909897), 'min_duration_us': np.float64(151.199), 'max_duration_us': np.float64(160.415)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'gpu_op_uid': 47431, 'count': 12, 'total_duration_us': np.float64(13.661999999999999), 'mean_duration_us': np.float64(1.1384999999999998), 'median_duration_us': np.float64(1.168), 'std_dev_duration_us': np.float64(0.18668846598901961), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.376)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'gpu_op_uid': 47441, 'count': 12, 'total_duration_us': np.float64(1890.9), 'mean_duration_us': np.float64(157.57500000000002), 'median_duration_us': np.float64(158.031), 'std_dev_duration_us': np.float64(2.2915636582909897), 'min_duration_us': np.float64(151.199), 'max_duration_us': np.float64(160.415)}]</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(10.656000000000002), 'mean_duration_us': np.float64(0.8880000000000002), 'median_duration_us': np.float64(0.8640000000000001), 'std_dev_duration_us': np.float64(0.10939835464941874), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.12)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(1501.144), 'mean_duration_us': np.float64(125.09533333333333), 'median_duration_us': np.float64(124.703), 'std_dev_duration_us': np.float64(1.0343101834341377), 'min_duration_us': np.float64(123.967), 'max_duration_us': np.float64(127.007)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'gpu_op_uid': 47319, 'count': 12, 'total_duration_us': np.float64(10.656000000000002), 'mean_duration_us': np.float64(0.8880000000000002), 'median_duration_us': np.float64(0.8640000000000001), 'std_dev_duration_us': np.float64(0.10939835464941874), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.12)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'gpu_op_uid': 47329, 'count': 12, 'total_duration_us': np.float64(1501.144), 'mean_duration_us': np.float64(125.09533333333333), 'median_duration_us': np.float64(124.703), 'std_dev_duration_us': np.float64(1.0343101834341377), 'min_duration_us': np.float64(123.967), 'max_duration_us': np.float64(127.007)}]</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -16491,7 +16491,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(10.401000000000003), 'mean_duration_us': np.float64(0.8667500000000002), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.11950113318849044), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.089)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(1468.15), 'mean_duration_us': np.float64(122.34583333333335), 'median_duration_us': np.float64(122.079), 'std_dev_duration_us': np.float64(0.8646479855345122), 'min_duration_us': np.float64(121.151), 'max_duration_us': np.float64(124.479)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'gpu_op_uid': 47219, 'count': 12, 'total_duration_us': np.float64(10.401000000000003), 'mean_duration_us': np.float64(0.8667500000000002), 'median_duration_us': np.float64(0.8), 'std_dev_duration_us': np.float64(0.11950113318849044), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.089)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'gpu_op_uid': 47229, 'count': 12, 'total_duration_us': np.float64(1468.15), 'mean_duration_us': np.float64(122.34583333333335), 'median_duration_us': np.float64(122.079), 'std_dev_duration_us': np.float64(0.8646479855345122), 'min_duration_us': np.float64(121.151), 'max_duration_us': np.float64(124.479)}]</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -16651,7 +16651,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_16x16_32x1_nn_align8&gt;(cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_16x16_32x1_nn_align8::Params)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(1300.504), 'mean_duration_us': np.float64(108.37533333333333), 'median_duration_us': np.float64(107.8715), 'std_dev_duration_us': np.float64(0.8493324175819239), 'min_duration_us': np.float64(107.583), 'max_duration_us': np.float64(109.599)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_16x16_32x1_nn_align8&gt;(cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_16x16_32x1_nn_align8::Params)', 'stream': 7, 'gpu_op_uid': 47261, 'count': 12, 'total_duration_us': np.float64(1300.504), 'mean_duration_us': np.float64(108.37533333333333), 'median_duration_us': np.float64(107.8715), 'std_dev_duration_us': np.float64(0.8493324175819239), 'min_duration_us': np.float64(107.583), 'max_duration_us': np.float64(109.599)}]</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -16811,7 +16811,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(23.326999999999998), 'mean_duration_us': np.float64(0.9719583333333333), 'median_duration_us': np.float64(0.96), 'std_dev_duration_us': np.float64(0.1973181608398533), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.439)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(1101.214), 'mean_duration_us': np.float64(45.883916666666664), 'median_duration_us': np.float64(45.936), 'std_dev_duration_us': np.float64(0.6211491310913646), 'min_duration_us': np.float64(44.992), 'max_duration_us': np.float64(47.008)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'gpu_op_uid': 47271, 'count': 24, 'total_duration_us': np.float64(23.326999999999998), 'mean_duration_us': np.float64(0.9719583333333333), 'median_duration_us': np.float64(0.96), 'std_dev_duration_us': np.float64(0.1973181608398533), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.439)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'gpu_op_uid': 47281, 'count': 24, 'total_duration_us': np.float64(1101.214), 'mean_duration_us': np.float64(45.883916666666664), 'median_duration_us': np.float64(45.936), 'std_dev_duration_us': np.float64(0.6211491310913646), 'min_duration_us': np.float64(44.992), 'max_duration_us': np.float64(47.008)}]</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -16971,7 +16971,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(10.337000000000003), 'mean_duration_us': np.float64(0.8614166666666669), 'median_duration_us': np.float64(0.7995000000000001), 'std_dev_duration_us': np.float64(0.12347837754935968), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.152)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(557.277), 'mean_duration_us': np.float64(46.439750000000004), 'median_duration_us': np.float64(46.432), 'std_dev_duration_us': np.float64(0.4246459554734984), 'min_duration_us': np.float64(45.951), 'max_duration_us': np.float64(47.295)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'gpu_op_uid': 47371, 'count': 12, 'total_duration_us': np.float64(10.337000000000003), 'mean_duration_us': np.float64(0.8614166666666669), 'median_duration_us': np.float64(0.7995000000000001), 'std_dev_duration_us': np.float64(0.12347837754935968), 'min_duration_us': np.float64(0.768), 'max_duration_us': np.float64(1.152)}, {'name': 'sm90_xmma_gemm_bf16bf16_bf16f32_f32_tn_n_tilesize128x128x64_warpgroupsize1x1x1_execute_segment_k_off_kernel__5x_cublas', 'stream': 7, 'gpu_op_uid': 47381, 'count': 12, 'total_duration_us': np.float64(557.277), 'mean_duration_us': np.float64(46.439750000000004), 'median_duration_us': np.float64(46.432), 'std_dev_duration_us': np.float64(0.4246459554734984), 'min_duration_us': np.float64(45.951), 'max_duration_us': np.float64(47.295)}]</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -17131,7 +17131,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_16x16_64x1_nn_align8&gt;(cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_16x16_64x1_nn_align8::Params)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(490.207), 'mean_duration_us': np.float64(40.85058333333333), 'median_duration_us': np.float64(40.7355), 'std_dev_duration_us': np.float64(0.4567669825949428), 'min_duration_us': np.float64(40.288), 'max_duration_us': np.float64(41.632)}]</t>
+          <t>[{'name': 'void cutlass::Kernel2&lt;cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_16x16_64x1_nn_align8&gt;(cutlass_80_wmma_tensorop_bf16_s161616gemm_bf16_16x16_64x1_nn_align8::Params)', 'stream': 7, 'gpu_op_uid': 47243, 'count': 12, 'total_duration_us': np.float64(490.207), 'mean_duration_us': np.float64(40.85058333333333), 'median_duration_us': np.float64(40.7355), 'std_dev_duration_us': np.float64(0.4567669825949428), 'min_duration_us': np.float64(40.288), 'max_duration_us': np.float64(41.632)}]</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -17287,7 +17287,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>[{'name': 'std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, false, true, true, false, 7, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(5.056), 'mean_duration_us': np.float64(5.056), 'median_duration_us': np.float64(5.056), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(5.056), 'max_duration_us': np.float64(5.056)}]</t>
+          <t>[{'name': 'std::enable_if&lt;!(false), void&gt;::type internal::gemvx::kernel&lt;int, int, __nv_bfloat16, __nv_bfloat16, __nv_bfloat16, float, false, true, true, false, 7, false, cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt; &gt;(cublasGemvParamsEx&lt;int, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16 const&gt;, cublasGemvTensorStridedBatched&lt;__nv_bfloat16&gt;, float&gt;)', 'stream': 7, 'gpu_op_uid': 50049, 'count': 1, 'total_duration_us': np.float64(5.056), 'mean_duration_us': np.float64(5.056), 'median_duration_us': np.float64(5.056), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(5.056), 'max_duration_us': np.float64(5.056)}]</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -17707,7 +17707,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>[{'name': 'Memset (Device)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(32.448), 'mean_duration_us': np.float64(32.448), 'median_duration_us': np.float64(32.448), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(32.448), 'max_duration_us': np.float64(32.448)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(281.343), 'mean_duration_us': np.float64(281.343), 'median_duration_us': np.float64(281.343), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(281.343), 'max_duration_us': np.float64(281.343)}, {'name': 'Memset (Device)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.336), 'mean_duration_us': np.float64(2.336), 'median_duration_us': np.float64(2.336), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.336), 'max_duration_us': np.float64(2.336)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(10.336), 'mean_duration_us': np.float64(10.336), 'median_duration_us': np.float64(10.336), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(10.336), 'max_duration_us': np.float64(10.336)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8&gt;(cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8::Params)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(863.099), 'mean_duration_us': np.float64(863.099), 'median_duration_us': np.float64(863.099), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(863.099), 'max_duration_us': np.float64(863.099)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(43.488), 'mean_duration_us': np.float64(43.488), 'median_duration_us': np.float64(43.488), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(43.488), 'max_duration_us': np.float64(43.488)}, {'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(64.864), 'mean_duration_us': np.float64(64.864), 'median_duration_us': np.float64(64.864), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(64.864), 'max_duration_us': np.float64(64.864)}]</t>
+          <t>[{'name': 'Memset (Device)', 'stream': 7, 'gpu_op_uid': 47151, 'count': 1, 'total_duration_us': np.float64(32.448), 'mean_duration_us': np.float64(32.448), 'median_duration_us': np.float64(32.448), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(32.448), 'max_duration_us': np.float64(32.448)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'gpu_op_uid': 47155, 'count': 1, 'total_duration_us': np.float64(281.343), 'mean_duration_us': np.float64(281.343), 'median_duration_us': np.float64(281.343), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(281.343), 'max_duration_us': np.float64(281.343)}, {'name': 'Memset (Device)', 'stream': 7, 'gpu_op_uid': 47159, 'count': 1, 'total_duration_us': np.float64(2.336), 'mean_duration_us': np.float64(2.336), 'median_duration_us': np.float64(2.336), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.336), 'max_duration_us': np.float64(2.336)}, {'name': 'void cudnn::engines_precompiled::nchwToNhwcKernel&lt;__nv_bfloat16, __nv_bfloat16, float, false, true, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nchw2nhwc_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'gpu_op_uid': 47163, 'count': 1, 'total_duration_us': np.float64(10.336), 'mean_duration_us': np.float64(10.336), 'median_duration_us': np.float64(10.336), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(10.336), 'max_duration_us': np.float64(10.336)}, {'name': 'void cutlass__5x_cudnn::Kernel&lt;cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8&gt;(cutlass_tensorop_bf16_s16816fprop_optimized_bf16_256x64_32x4_nhwc_align8::Params)', 'stream': 7, 'gpu_op_uid': 47171, 'count': 1, 'total_duration_us': np.float64(863.099), 'mean_duration_us': np.float64(863.099), 'median_duration_us': np.float64(863.099), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(863.099), 'max_duration_us': np.float64(863.099)}, {'name': 'void cudnn::engines_precompiled::nhwcToNchwKernel&lt;__nv_bfloat16, __nv_bfloat16, float, true, false, (cudnnKernelDataType_t)0&gt;(cudnn::engines_precompiled::nhwc2nchw_params_t&lt;float&gt;, __nv_bfloat16 const*, __nv_bfloat16*)', 'stream': 7, 'gpu_op_uid': 47177, 'count': 1, 'total_duration_us': np.float64(43.488), 'mean_duration_us': np.float64(43.488), 'median_duration_us': np.float64(43.488), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(43.488), 'max_duration_us': np.float64(43.488)}, {'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 47181, 'count': 1, 'total_duration_us': np.float64(64.864), 'mean_duration_us': np.float64(64.864), 'median_duration_us': np.float64(64.864), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(64.864), 'max_duration_us': np.float64(64.864)}]</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -17769,7 +17769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL8"/>
+  <dimension ref="A1:AJ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17780,185 +17780,175 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>param: shape_in1</t>
+          <t>param: op_shape</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>param: shape_in2</t>
+          <t>param: dtype_in_out</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>param: dtype_in1_in2_out</t>
+          <t>param: stride_input</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>param: stride_input1</t>
+          <t>param: stride_output</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>param: stride_input2</t>
+          <t>GFLOPS_first</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>param: stride_output</t>
+          <t>Data Moved (MB)_first</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>GFLOPS_first</t>
+          <t>FLOPS/Byte_first</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Data Moved (MB)_first</t>
+          <t>TB/s_mean</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>FLOPS/Byte_first</t>
+          <t>TB/s_median</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>TB/s_mean</t>
+          <t>TB/s_std</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>TB/s_median</t>
+          <t>TB/s_min</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>TB/s_std</t>
+          <t>TB/s_max</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>TB/s_min</t>
+          <t>TFLOPS/s_mean</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>TB/s_max</t>
+          <t>TFLOPS/s_median</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_mean</t>
+          <t>TFLOPS/s_std</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_median</t>
+          <t>TFLOPS/s_min</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_std</t>
+          <t>TFLOPS/s_max</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_min</t>
+          <t>process_name_first</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>TFLOPS/s_max</t>
+          <t>process_label_first</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>process_name_first</t>
+          <t>thread_name_first</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>process_label_first</t>
+          <t>Compute Spec</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>thread_name_first</t>
+          <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Compute Spec</t>
+          <t>trunc_kernel_details</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>kernel_details__summarize_kernel_stats</t>
+          <t>Input Dims_first</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>trunc_kernel_details</t>
+          <t>Input type_first</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Input Dims_first</t>
+          <t>Input Strides_first</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Input type_first</t>
+          <t>Concrete Inputs_first</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>Input Strides_first</t>
+          <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>Concrete Inputs_first</t>
+          <t>Kernel Time (µs)_median</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_mean</t>
+          <t>Kernel Time (µs)_std</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_median</t>
+          <t>Kernel Time (µs)_min</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_std</t>
+          <t>Kernel Time (µs)_max</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_min</t>
+          <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>Kernel Time (µs)_max</t>
+          <t>name_count</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
-        <is>
-          <t>Kernel Time (µs)_sum</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>name_count</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -17967,1005 +17957,1771 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>aten::mul</t>
+          <t>aten::copy_</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(8, 12, 3137, 3137)</t>
+          <t>(1, 128, 3, 224, 224)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>()</t>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'double', None)</t>
+          <t>(19267584, 150528, 50176, 224, 1)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(118089228, 9840769, 3137, 1)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>(19267584, 150528, 50176, 224, 1)</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.019267584</v>
+      </c>
+      <c r="G2" t="n">
+        <v>73.5</v>
+      </c>
       <c r="H2" t="n">
-        <v>0.944713824</v>
+        <v>0.25</v>
       </c>
       <c r="I2" t="n">
-        <v>3603.797248840332</v>
+        <v>0.02226592510813797</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2499999994707392</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2.926464779143708</v>
-      </c>
+        <v>0.02226592510813797</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>2.926783636974142</v>
+        <v>0.02226592510813797</v>
       </c>
       <c r="M2" t="n">
-        <v>0.002087325090309445</v>
+        <v>0.02226592510813797</v>
       </c>
       <c r="N2" t="n">
-        <v>2.923668106984001</v>
+        <v>0.005566481277034492</v>
       </c>
       <c r="O2" t="n">
-        <v>2.930124331900724</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.7316161932370641</v>
-      </c>
+        <v>0.005566481277034492</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>0.7316959076945038</v>
+        <v>0.005566481277034492</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0005218312714726101</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.7309170251986173</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.7325310814243809</v>
+        <v>0.005566481277034492</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>python3</t>
+          <t>thread 17751 (python3)</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>vector_bf16</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>thread 17751 (python3)</t>
+          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'gpu_op_uid': 47137, 'count': 1, 'total_duration_us': np.float64(3461.358), 'mean_duration_us': np.float64(3461.358), 'median_duration_us': np.float64(3461.358), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3461.358), 'max_duration_us': np.float64(3461.358)}]</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>vector_bf16</t>
+          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'mean_duration_us': np.float64(3461.36)}]</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(15495.243999999999), 'mean_duration_us': np.float64(1291.2703333333332), 'median_duration_us': np.float64(1291.129), 'std_dev_duration_us': np.float64(0.8817396945181291), 'min_duration_us': np.float64(1289.657), 'max_duration_us': np.float64(1292.505)}]</t>
+          <t>[[1, 128, 3, 224, 224], [1, 128, 3, 224, 224], []]</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': np.float64(1291.27)}]</t>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>[[8, 12, 3137, 3137], []]</t>
+          <t>[[19267584, 150528, 50176, 224, 1], [19267584, 150528, 50176, 224, 1], []]</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>['c10::BFloat16', 'double']</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>[[118089228, 9840769, 3137, 1], []]</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>['', '']</t>
-        </is>
-      </c>
-      <c r="AE2" t="n">
-        <v>1291.270304361979</v>
-      </c>
+          <t>['', '', 'False']</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>3461.35791015625</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>3461.35791015625</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>1291.129028320312</v>
+        <v>3461.35791015625</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.92091938935065</v>
+        <v>3461.35791015625</v>
       </c>
       <c r="AH2" t="n">
-        <v>1289.656982421875</v>
+        <v>3461.35791015625</v>
       </c>
       <c r="AI2" t="n">
-        <v>1292.5048828125</v>
+        <v>1</v>
       </c>
       <c r="AJ2" t="n">
-        <v>15495.24365234375</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>260</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>aten::add</t>
+          <t>aten::copy_</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>(1, 25089, 768)</t>
+          <t>(8, 12, 64, 3137)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(1, 25089, 768)</t>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
+          <t>(2409216, 200768, 3137, 1)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>(19268352, 768, 1)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>(19268352, 768, 1)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>(7227648, 64, 1, 2304)</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.019273728</v>
+      </c>
+      <c r="G3" t="n">
+        <v>73.5234375</v>
+      </c>
       <c r="H3" t="n">
-        <v>0.019268352</v>
+        <v>0.25</v>
       </c>
       <c r="I3" t="n">
-        <v>110.25439453125</v>
+        <v>0.5011573421889868</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.5012429309440907</v>
       </c>
       <c r="K3" t="n">
-        <v>3.116712998732709</v>
+        <v>0.0005911931389301384</v>
       </c>
       <c r="L3" t="n">
-        <v>3.086642791345411</v>
+        <v>0.5003593038782586</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1319357780554476</v>
+        <v>0.501919680888061</v>
       </c>
       <c r="N3" t="n">
-        <v>2.942040177141579</v>
+        <v>0.1252893355472467</v>
       </c>
       <c r="O3" t="n">
-        <v>3.299371664334884</v>
+        <v>0.1253107327360227</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5194521664554514</v>
+        <v>0.0001477982847325346</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5144404652242351</v>
+        <v>0.1250898259695646</v>
       </c>
       <c r="R3" t="n">
-        <v>0.02198929634257462</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.4903400295235965</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.5498952773891473</v>
+        <v>0.1254799202220153</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>python3</t>
+          <t>thread 17751 (python3)</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>vector_bf16</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>thread 17751 (python3)</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 47337, 'count': 12, 'total_duration_us': np.float64(1846.007), 'mean_duration_us': np.float64(153.83391666666668), 'median_duration_us': np.float64(153.8075), 'std_dev_duration_us': np.float64(0.17379991289475016), 'min_duration_us': np.float64(153.6), 'max_duration_us': np.float64(154.079)}]</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>vector_bf16</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(153.83)}]</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(891.774), 'mean_duration_us': np.float64(37.15725), 'median_duration_us': np.float64(37.471999999999994), 'std_dev_duration_us': np.float64(1.5359198723132224), 'min_duration_us': np.float64(35.04), 'max_duration_us': np.float64(39.296)}]</t>
+          <t>[[8, 12, 64, 3137], [8, 12, 64, 3137], []]</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(37.16)}]</t>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>[[1, 25089, 768], [1, 25089, 768], []]</t>
+          <t>[[2409216, 200768, 3137, 1], [7227648, 64, 1, 2304], []]</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>[[19268352, 768, 1], [19268352, 768, 1], []]</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>['', '', '1']</t>
-        </is>
+          <t>['', '', 'False']</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>153.8339436848958</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>153.8074951171875</v>
       </c>
       <c r="AE3" t="n">
-        <v>37.15723673502604</v>
+        <v>0.1814923269919053</v>
       </c>
       <c r="AF3" t="n">
-        <v>37.4720458984375</v>
+        <v>153.60009765625</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.568952326542583</v>
+        <v>154.0791015625</v>
       </c>
       <c r="AH3" t="n">
-        <v>35.0400390625</v>
+        <v>1846.00732421875</v>
       </c>
       <c r="AI3" t="n">
-        <v>39.2958984375</v>
+        <v>12</v>
       </c>
       <c r="AJ3" t="n">
-        <v>891.773681640625</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>324</v>
+        <v>256</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>aten::add</t>
+          <t>aten::copy_</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>(1, 25088, 768)</t>
+          <t>(8, 12, 3137, 64)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>(1, 25088, 768)</t>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
+          <t>(2409216, 200768, 64, 1)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>(19268352, 768, 1)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>(19267584, 768, 1)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>(7227648, 64, 2304, 1)</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.019273728</v>
+      </c>
+      <c r="G4" t="n">
+        <v>73.5234375</v>
+      </c>
       <c r="H4" t="n">
-        <v>0.019267584</v>
+        <v>0.25</v>
       </c>
       <c r="I4" t="n">
-        <v>110.25</v>
+        <v>1.304559223068945</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1666666666666667</v>
+        <v>1.303000720317353</v>
       </c>
       <c r="K4" t="n">
-        <v>2.960838354303617</v>
+        <v>0.01715970100611623</v>
       </c>
       <c r="L4" t="n">
-        <v>2.966065314624006</v>
+        <v>1.280159399496499</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03684353277674083</v>
+        <v>1.331060358927668</v>
       </c>
       <c r="N4" t="n">
-        <v>2.894766682463412</v>
+        <v>0.3261398057672362</v>
       </c>
       <c r="O4" t="n">
-        <v>3.008062308289448</v>
+        <v>0.3257501800793383</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4934730590506029</v>
+        <v>0.004289925251529056</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4943442191040012</v>
+        <v>0.3200398498741249</v>
       </c>
       <c r="R4" t="n">
-        <v>0.006140588796123471</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.482461113743902</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.5013437180482413</v>
+        <v>0.332765089731917</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>python3</t>
+          <t>thread 17751 (python3)</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>vector_bf16</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>thread 17751 (python3)</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 47333, 'count': 24, 'total_duration_us': np.float64(1418.552), 'mean_duration_us': np.float64(59.10633333333333), 'median_duration_us': np.float64(59.167500000000004), 'std_dev_duration_us': np.float64(0.7604596563190504), 'min_duration_us': np.float64(57.92), 'max_duration_us': np.float64(60.223)}]</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>vector_bf16</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(59.11)}]</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(468.6050000000001), 'mean_duration_us': np.float64(39.05041666666667), 'median_duration_us': np.float64(38.976), 'std_dev_duration_us': np.float64(0.46841407222195597), 'min_duration_us': np.float64(38.432), 'max_duration_us': np.float64(39.936)}]</t>
+          <t>[[8, 12, 3137, 64], [8, 12, 3137, 64], []]</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(39.05)}]</t>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>[[1, 25088, 768], [1, 25088, 768], []]</t>
+          <t>[[2409216, 200768, 64, 1], [7227648, 64, 2304, 1], []]</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>[[19268352, 768, 1], [19267584, 768, 1], []]</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>['', '', '1']</t>
-        </is>
+          <t>['', '', 'False']</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>59.10631306966146</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>59.16748046875</v>
       </c>
       <c r="AE4" t="n">
-        <v>39.05043538411459</v>
+        <v>0.7768103961300407</v>
       </c>
       <c r="AF4" t="n">
-        <v>38.97607421875</v>
+        <v>57.919921875</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.4892606085061316</v>
+        <v>60.222900390625</v>
       </c>
       <c r="AH4" t="n">
-        <v>38.431884765625</v>
+        <v>1418.551513671875</v>
       </c>
       <c r="AI4" t="n">
-        <v>39.93603515625</v>
+        <v>24</v>
       </c>
       <c r="AJ4" t="n">
-        <v>468.605224609375</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>180</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>aten::add</t>
+          <t>aten::copy_</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>(196, 128, 768)</t>
+          <t>(3136, 12, 8, 64)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>(1, 128, 768)</t>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
+          <t>(6144, 512, 64, 1)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>(768, 151296, 1)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>(98304, 1, 128)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>(18432, 64, 2304, 1)</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.019267584</v>
+      </c>
+      <c r="G5" t="n">
+        <v>73.5</v>
+      </c>
       <c r="H5" t="n">
-        <v>0.019267584</v>
+        <v>0.25</v>
       </c>
       <c r="I5" t="n">
-        <v>73.6875</v>
+        <v>1.321548671940372</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2493638676844784</v>
+        <v>1.317717016856813</v>
       </c>
       <c r="K5" t="n">
-        <v>0.897617029201552</v>
+        <v>0.03358092858653137</v>
       </c>
       <c r="L5" t="n">
-        <v>0.897617029201552</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+        <v>1.281091233309661</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.362269598180649</v>
+      </c>
       <c r="N5" t="n">
-        <v>0.897617029201552</v>
+        <v>0.330387167985093</v>
       </c>
       <c r="O5" t="n">
-        <v>0.897617029201552</v>
+        <v>0.3294292542142033</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2238332541011504</v>
+        <v>0.008395232146632842</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2238332541011504</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="n">
-        <v>0.2238332541011504</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.2238332541011504</v>
+        <v>0.3202728083274152</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.3405673995451623</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>python3</t>
+          <t>thread 17751 (python3)</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>vector_bf16</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>thread 17751 (python3)</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 47233, 'count': 24, 'total_duration_us': np.float64(1400.504), 'mean_duration_us': np.float64(58.35433333333333), 'median_duration_us': np.float64(58.4955), 'std_dev_duration_us': np.float64(1.4517576320523424), 'min_duration_us': np.float64(56.575), 'max_duration_us': np.float64(60.16)}]</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>vector_bf16</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(58.35)}]</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(86.08), 'mean_duration_us': np.float64(86.08), 'median_duration_us': np.float64(86.08), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(86.08), 'max_duration_us': np.float64(86.08)}]</t>
+          <t>[[3136, 12, 8, 64], [3136, 12, 8, 64], []]</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(86.08)}]</t>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>[[196, 128, 768], [1, 128, 768], []]</t>
+          <t>[[6144, 512, 64, 1], [18432, 64, 2304, 1], []]</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>[[768, 151296, 1], [98304, 1, 128], []]</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>['', '', '1']</t>
-        </is>
+          <t>['', '', 'False']</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>58.35430908203125</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>58.4954833984375</v>
       </c>
       <c r="AE5" t="n">
-        <v>86.080078125</v>
+        <v>1.483017836999234</v>
       </c>
       <c r="AF5" t="n">
-        <v>86.080078125</v>
-      </c>
-      <c r="AG5" t="inlineStr"/>
+        <v>56.574951171875</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>60.159912109375</v>
+      </c>
       <c r="AH5" t="n">
-        <v>86.080078125</v>
+        <v>1400.50341796875</v>
       </c>
       <c r="AI5" t="n">
-        <v>86.080078125</v>
+        <v>24</v>
       </c>
       <c r="AJ5" t="n">
-        <v>86.080078125</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>57</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>aten::add_</t>
+          <t>aten::copy_</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>(128, 768, 14, 14)</t>
+          <t>(3136, 8, 12, 64)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>(1, 768, 1, 1)</t>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
+          <t>(6144, 768, 64, 1)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(150528, 196, 14, 1)</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>(768, 1, 1, 1)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>(6144, 64, 512, 1)</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.019267584</v>
+      </c>
+      <c r="G6" t="n">
+        <v>73.5</v>
+      </c>
       <c r="H6" t="n">
-        <v>0.019267584</v>
+        <v>0.25</v>
       </c>
       <c r="I6" t="n">
-        <v>73.50146484375</v>
+        <v>1.346541254451492</v>
       </c>
       <c r="J6" t="n">
-        <v>0.249995017637563</v>
+        <v>1.346640415063802</v>
       </c>
       <c r="K6" t="n">
-        <v>1.188206952315353</v>
+        <v>0.00649169023188425</v>
       </c>
       <c r="L6" t="n">
-        <v>1.188206952315353</v>
-      </c>
-      <c r="M6" t="inlineStr"/>
+        <v>1.335799292730712</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.35460602061431</v>
+      </c>
       <c r="N6" t="n">
-        <v>1.188206952315353</v>
+        <v>0.3366353136128731</v>
       </c>
       <c r="O6" t="n">
-        <v>1.188206952315353</v>
+        <v>0.3366601037659506</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2970458180011518</v>
+        <v>0.001622922557971063</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2970458180011518</v>
-      </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="n">
-        <v>0.2970458180011518</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.2970458180011518</v>
+        <v>0.333949823182678</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.3386515051535775</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>python3</t>
+          <t>thread 17751 (python3)</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>vector_bf16</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>thread 17751 (python3)</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 47265, 'count': 12, 'total_duration_us': np.float64(686.844), 'mean_duration_us': np.float64(57.237), 'median_duration_us': np.float64(57.2315), 'std_dev_duration_us': np.float64(0.2646696053573195), 'min_duration_us': np.float64(56.895), 'max_duration_us': np.float64(57.696)}]</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>vector_bf16</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(57.24)}]</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(64.864), 'mean_duration_us': np.float64(64.864), 'median_duration_us': np.float64(64.864), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(64.864), 'max_duration_us': np.float64(64.864)}]</t>
+          <t>[[3136, 8, 12, 64], [3136, 8, 12, 64], []]</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(64.86)}]</t>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>[[128, 768, 14, 14], [1, 768, 1, 1], []]</t>
+          <t>[[6144, 768, 64, 1], [6144, 64, 512, 1], []]</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>[[150528, 196, 14, 1], [768, 1, 1, 1], []]</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>['', '', '1']</t>
-        </is>
+          <t>['', '', 'False']</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>57.23699951171875</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>57.2315673828125</v>
       </c>
       <c r="AE6" t="n">
-        <v>64.864013671875</v>
+        <v>0.2764603445241264</v>
       </c>
       <c r="AF6" t="n">
-        <v>64.864013671875</v>
-      </c>
-      <c r="AG6" t="inlineStr"/>
+        <v>56.89501953125</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>57.696044921875</v>
+      </c>
       <c r="AH6" t="n">
-        <v>64.864013671875</v>
+        <v>686.843994140625</v>
       </c>
       <c r="AI6" t="n">
-        <v>64.864013671875</v>
+        <v>12</v>
       </c>
       <c r="AJ6" t="n">
-        <v>64.864013671875</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>18</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>aten::mul</t>
+          <t>aten::copy_</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>(3136, 12, 8, 8)</t>
+          <t>(8, 3137, 12, 64)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>()</t>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'double', None)</t>
+          <t>(2409216, 768, 64, 1)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>(768, 64, 8, 1)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>()</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>(2409216, 64, 200768, 1)</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.019273728</v>
+      </c>
+      <c r="G7" t="n">
+        <v>73.5234375</v>
+      </c>
       <c r="H7" t="n">
-        <v>0.002408448</v>
+        <v>0.25</v>
       </c>
       <c r="I7" t="n">
-        <v>9.187507629394531</v>
+        <v>1.36424329615657</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2499997923976001</v>
+        <v>1.365007173751196</v>
       </c>
       <c r="K7" t="n">
-        <v>1.913497870540554</v>
+        <v>0.004485938567823921</v>
       </c>
       <c r="L7" t="n">
-        <v>1.942313683796023</v>
+        <v>1.354253462185379</v>
       </c>
       <c r="M7" t="n">
-        <v>0.08665362827660592</v>
+        <v>1.371236835246147</v>
       </c>
       <c r="N7" t="n">
-        <v>1.65416243135611</v>
+        <v>0.3410608240391426</v>
       </c>
       <c r="O7" t="n">
-        <v>1.967689478408298</v>
+        <v>0.3412517934377991</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4783740703883884</v>
+        <v>0.00112148464195598</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4855780177200236</v>
+        <v>0.3385633655463446</v>
       </c>
       <c r="R7" t="n">
-        <v>0.02166338907965028</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.4135402644309369</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.4919219611050165</v>
+        <v>0.3428092088115369</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>python3</t>
+          <t>thread 17751 (python3)</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>vector_bf16</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>thread 17751 (python3)</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 47365, 'count': 12, 'total_duration_us': np.float64(678.1399999999999), 'mean_duration_us': np.float64(56.511666666666656), 'median_duration_us': np.float64(56.4795), 'std_dev_duration_us': np.float64(0.17831869098766825), 'min_duration_us': np.float64(56.223), 'max_duration_us': np.float64(56.928)}]</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>vector_bf16</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(56.51)}]</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(60.544), 'mean_duration_us': np.float64(5.045333333333333), 'median_duration_us': np.float64(4.96), 'std_dev_duration_us': np.float64(0.24591236017916807), 'min_duration_us': np.float64(4.896), 'max_duration_us': np.float64(5.824)}]</t>
+          <t>[[8, 3137, 12, 64], [8, 3137, 12, 64], []]</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': np.float64(5.05)}]</t>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>[[3136, 12, 8, 8], []]</t>
+          <t>[[2409216, 768, 64, 1], [2409216, 64, 200768, 1], []]</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>['c10::BFloat16', 'double']</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>[[768, 64, 8, 1], []]</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>['', '']</t>
-        </is>
+          <t>['', '', 'False']</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>56.51167805989584</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>56.4794921875</v>
       </c>
       <c r="AE7" t="n">
-        <v>5.045308430989583</v>
+        <v>0.1862679325817069</v>
       </c>
       <c r="AF7" t="n">
-        <v>4.9599609375</v>
+        <v>56.222900390625</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.25685255038906</v>
+        <v>56.927978515625</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.89599609375</v>
+        <v>678.14013671875</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.823974609375</v>
+        <v>12</v>
       </c>
       <c r="AJ7" t="n">
-        <v>60.543701171875</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>124</v>
+        <v>285</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>aten::add</t>
+          <t>aten::copy_</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>(128, 197, 768)</t>
+          <t>(1, 224, 14, 8, 768)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>(1, 197, 768)</t>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
+          <t>(19267584, 86016, 6144, 768, 1)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>(151296, 768, 1)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>(151296, 768, 1)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>(19273728, 10752, 768, 2409216, 1)</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0.019267584</v>
+      </c>
+      <c r="G8" t="n">
+        <v>73.5</v>
+      </c>
       <c r="H8" t="n">
-        <v>0.019365888</v>
+        <v>0.25</v>
       </c>
       <c r="I8" t="n">
-        <v>74.16357421875</v>
+        <v>1.449765337831095</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2490272373540856</v>
+        <v>1.449124642695606</v>
       </c>
       <c r="K8" t="n">
-        <v>1.440569687238257</v>
+        <v>0.008992930670082923</v>
       </c>
       <c r="L8" t="n">
-        <v>1.440569687238257</v>
-      </c>
-      <c r="M8" t="inlineStr"/>
+        <v>1.436162906973359</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.464105115442947</v>
+      </c>
       <c r="N8" t="n">
-        <v>1.440569687238257</v>
+        <v>0.3624413344577738</v>
       </c>
       <c r="O8" t="n">
-        <v>1.440569687238257</v>
+        <v>0.3622811606739015</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3587410894289824</v>
+        <v>0.002248232667520731</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3587410894289824</v>
-      </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="n">
-        <v>0.3587410894289824</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.3587410894289824</v>
+        <v>0.3590407267433396</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.3660262788607366</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
+          <t>thread 17751 (python3)</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 47389, 'count': 12, 'total_duration_us': np.float64(637.9490000000001), 'mean_duration_us': np.float64(53.16241666666667), 'median_duration_us': np.float64(53.184), 'std_dev_duration_us': np.float64(0.31582021740576044), 'min_duration_us': np.float64(52.64), 'max_duration_us': np.float64(53.664)}]</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(53.16)}]</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>[[1, 224, 14, 8, 768], [1, 224, 14, 8, 768], []]</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>[[19267584, 86016, 6144, 768, 1], [19273728, 10752, 768, 2409216, 1], []]</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>['', '', 'False']</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>53.16243489583334</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>53.18408203125</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.3298869750019682</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>52.639892578125</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>53.6640625</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>637.94921875</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>(3136, 12, 64, 8)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>(6144, 512, 8, 1)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>(18432, 64, 1, 2304)</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0.019267584</v>
+      </c>
+      <c r="G9" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.509537166523619</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.509539221380834</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01116693498626933</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.493149131610688</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.526292843599513</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.3773842916309048</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.3773848053452085</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.002791733746567333</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.373287282902672</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.3815732108998782</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>thread 17751 (python3)</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(53.983), 'mean_duration_us': np.float64(53.983), 'median_duration_us': np.float64(53.983), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(53.983), 'max_duration_us': np.float64(53.983)}]</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(53.98)}]</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>[[128, 197, 768], [1, 197, 768], []]</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 47237, 'count': 12, 'total_duration_us': np.float64(612.698), 'mean_duration_us': np.float64(51.058166666666665), 'median_duration_us': np.float64(51.055499999999995), 'std_dev_duration_us': np.float64(0.36143575577902604), 'min_duration_us': np.float64(50.495), 'max_duration_us': np.float64(51.616)}]</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(51.06)}]</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>[[3136, 12, 64, 8], [3136, 12, 64, 8], []]</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>[[151296, 768, 1], [151296, 768, 1], []]</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>['', '', '1']</t>
-        </is>
-      </c>
-      <c r="AE8" t="n">
-        <v>53.98291015625</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>53.98291015625</v>
-      </c>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="n">
-        <v>53.98291015625</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>53.98291015625</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>53.98291015625</v>
-      </c>
-      <c r="AK8" t="n">
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>[[6144, 512, 8, 1], [18432, 64, 1, 2304], []]</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>['', '', 'False']</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>51.05816650390625</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>51.0555419921875</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.3774848472435202</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>50.4951171875</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>51.615966796875</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>612.697998046875</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>(1, 196, 128, 768)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>(19267584, 98304, 768, 1)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>(150528, 768, 150528, 1)</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0.019267584</v>
+      </c>
+      <c r="G10" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.489457525164785</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.489457525164785</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>1.489457525164785</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.489457525164785</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.3723643812911963</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.3723643812911963</v>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="n">
+        <v>0.3723643812911963</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.3723643812911963</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>thread 17751 (python3)</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 47205, 'count': 1, 'total_duration_us': np.float64(51.744), 'mean_duration_us': np.float64(51.744), 'median_duration_us': np.float64(51.744), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(51.744), 'max_duration_us': np.float64(51.744)}]</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(51.74)}]</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>[[1, 196, 128, 768], [1, 196, 128, 768], []]</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>[[19267584, 98304, 768, 1], [150528, 768, 150528, 1], []]</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>['', '', 'False']</t>
+        </is>
+      </c>
+      <c r="AC10" t="n">
+        <v>51.743896484375</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>51.743896484375</v>
+      </c>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="n">
+        <v>51.743896484375</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>51.743896484375</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>51.743896484375</v>
+      </c>
+      <c r="AI10" t="n">
         <v>1</v>
       </c>
-      <c r="AL8" t="n">
-        <v>26</v>
+      <c r="AJ10" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>(1, 8, 1, 1, 1, 768)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>(6144, 768, 768, 6144, 768, 1)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>(0, 0, 19268352, 19268352, 768, 1)</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>6.144e-06</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0234375</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.007097606117564984</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.006981779442363712</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0004125868896499309</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.006736935885423638</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.008347565801476076</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.001774401529391246</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.001745444860590928</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.0001031467224124827</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.00168423397135591</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.002086891450369019</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>thread 17751 (python3)</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 47305, 'count': 12, 'total_duration_us': np.float64(41.66400000000001), 'mean_duration_us': np.float64(3.472000000000001), 'median_duration_us': np.float64(3.52), 'std_dev_duration_us': np.float64(0.17008233300375442), 'min_duration_us': np.float64(2.944), 'max_duration_us': np.float64(3.648)}]</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(3.47)}]</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>[[1, 8, 1, 1, 1, 768], [1, 8, 1, 1, 1, 768], []]</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>[[6144, 768, 768, 6144, 768, 1], [0, 0, 19268352, 19268352, 768, 1], []]</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>['', '', 'False']</t>
+        </is>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.472025553385417</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3.52001953125</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.17761358856306</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.944091796875</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3.64794921875</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>41.664306640625</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>(1, 768, 8)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>(6144, 8, 1)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>(6144, 1, 768)</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>6.144e-06</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0234375</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.006145500366300367</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.006145500366300367</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0.006145500366300367</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.006145500366300367</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.001536375091575092</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.001536375091575092</v>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="n">
+        <v>0.001536375091575092</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.001536375091575092</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>thread 17751 (python3)</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 47193, 'count': 1, 'total_duration_us': np.float64(3.999), 'mean_duration_us': np.float64(3.999), 'median_duration_us': np.float64(3.999), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.999), 'max_duration_us': np.float64(3.999)}]</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(4.0)}]</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>[[1, 768, 8], [1, 768, 8], []]</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>[[6144, 8, 1], [6144, 1, 768], []]</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>['', '', 'False']</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.9990234375</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.9990234375</v>
+      </c>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="n">
+        <v>3.9990234375</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>3.9990234375</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>3.9990234375</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>(1, 400)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>(400, 1)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>(400, 1)</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>4e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.00152587890625</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.0005747259493115847</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.0005747259493115847</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>0.0005747259493115847</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.0005747259493115847</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.0001436814873278962</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.0001436814873278962</v>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="n">
+        <v>0.0001436814873278962</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.0001436814873278962</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>thread 17751 (python3)</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'gpu_op_uid': 50053, 'count': 1, 'total_duration_us': np.float64(2.784), 'mean_duration_us': np.float64(2.784), 'median_duration_us': np.float64(2.784), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.784), 'max_duration_us': np.float64(2.784)}]</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': np.float64(2.78)}]</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>[[1, 400], [1, 400], []]</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>[[400, 1], [400, 1], []]</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>['', '', 'False']</t>
+        </is>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.783935546875</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.783935546875</v>
+      </c>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="n">
+        <v>2.783935546875</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.783935546875</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>2.783935546875</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>3531</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>aten::copy_</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>(1, 128, 3, 224, 224)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>('c10::BFloat16', 'float')</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>(19267584, 150528, 50176, 224, 1)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>(19267584, 150528, 50176, 224, 1)</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.019267584</v>
+      </c>
+      <c r="G14" t="n">
+        <v>110.25</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>python3</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>thread 17751 (python3)</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>vector_bf16</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>[[1, 128, 3, 224, 224], [1, 128, 3, 224, 224], []]</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>['c10::BFloat16', 'float', 'Scalar']</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>[[19267584, 150528, 50176, 224, 1], [19267584, 150528, 50176, 224, 1], []]</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>['', '', 'False']</t>
+        </is>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -18979,7 +19735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ14"/>
+  <dimension ref="A1:AL8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18990,175 +19746,185 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>param: op_shape</t>
+          <t>param: shape_in1</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>param: dtype_in_out</t>
+          <t>param: shape_in2</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>param: stride_input</t>
+          <t>param: dtype_in1_in2_out</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>param: stride_input1</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>param: stride_input2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>param: stride_output</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>GFLOPS_first</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Data Moved (MB)_first</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>FLOPS/Byte_first</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>TB/s_mean</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>TB/s_median</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>TB/s_std</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>TB/s_min</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>TB/s_max</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>TFLOPS/s_mean</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>TFLOPS/s_median</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>TFLOPS/s_std</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>TFLOPS/s_min</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>TFLOPS/s_max</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>process_name_first</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>process_label_first</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>thread_name_first</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Compute Spec</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>kernel_details__summarize_kernel_stats</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>trunc_kernel_details</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Input Dims_first</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Input type_first</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Input Strides_first</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Concrete Inputs_first</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_mean</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_median</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_std</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_min</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_max</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Kernel Time (µs)_sum</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>name_count</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>UID_first</t>
         </is>
@@ -19167,1771 +19933,1005 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>aten::copy_</t>
+          <t>aten::mul</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(1, 128, 3, 224, 224)</t>
+          <t>(8, 12, 3137, 3137)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+          <t>()</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(19267584, 150528, 50176, 224, 1)</t>
+          <t>('c10::BFloat16', 'double', None)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(19267584, 150528, 50176, 224, 1)</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>0.019267584</v>
-      </c>
-      <c r="G2" t="n">
-        <v>73.5</v>
-      </c>
+          <t>(118089228, 9840769, 3137, 1)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>()</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.25</v>
+        <v>0.944713824</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02226592510813797</v>
+        <v>3603.797248840332</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02226592510813797</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
+        <v>0.2499999994707392</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.926464779143708</v>
+      </c>
       <c r="L2" t="n">
-        <v>0.02226592510813797</v>
+        <v>2.926783636974142</v>
       </c>
       <c r="M2" t="n">
-        <v>0.02226592510813797</v>
+        <v>0.002087325090309445</v>
       </c>
       <c r="N2" t="n">
-        <v>0.005566481277034492</v>
+        <v>2.923668106984001</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005566481277034492</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
+        <v>2.930124331900724</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.7316161932370641</v>
+      </c>
       <c r="Q2" t="n">
-        <v>0.005566481277034492</v>
+        <v>0.7316959076945038</v>
       </c>
       <c r="R2" t="n">
-        <v>0.005566481277034492</v>
-      </c>
-      <c r="S2" t="inlineStr">
+        <v>0.0005218312714726101</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.7309170251986173</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.7325310814243809</v>
+      </c>
+      <c r="U2" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>thread 17751 (python3)</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3461.358), 'mean_duration_us': np.float64(3461.358), 'median_duration_us': np.float64(3461.358), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3461.358), 'max_duration_us': np.float64(3461.358)}]</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>[{'name': 'Memcpy HtoD (Pageable -&gt; Device)', 'stream': 7, 'mean_duration_us': np.float64(3461.36)}]</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[[1, 128, 3, 224, 224], [1, 128, 3, 224, 224], []]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'gpu_op_uid': 47347, 'count': 12, 'total_duration_us': np.float64(15495.243999999999), 'mean_duration_us': np.float64(1291.2703333333332), 'median_duration_us': np.float64(1291.129), 'std_dev_duration_us': np.float64(0.8817396945181291), 'min_duration_us': np.float64(1289.657), 'max_duration_us': np.float64(1292.505)}]</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': np.float64(1291.27)}]</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>[[19267584, 150528, 50176, 224, 1], [19267584, 150528, 50176, 224, 1], []]</t>
+          <t>[[8, 12, 3137, 3137], []]</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>['', '', 'False']</t>
-        </is>
-      </c>
-      <c r="AC2" t="n">
-        <v>3461.35791015625</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>3461.35791015625</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
+          <t>['c10::BFloat16', 'double']</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>[[118089228, 9840769, 3137, 1], []]</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>['', '']</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>1291.270304361979</v>
+      </c>
       <c r="AF2" t="n">
-        <v>3461.35791015625</v>
+        <v>1291.129028320312</v>
       </c>
       <c r="AG2" t="n">
-        <v>3461.35791015625</v>
+        <v>0.92091938935065</v>
       </c>
       <c r="AH2" t="n">
-        <v>3461.35791015625</v>
+        <v>1289.656982421875</v>
       </c>
       <c r="AI2" t="n">
-        <v>1</v>
+        <v>1292.5048828125</v>
       </c>
       <c r="AJ2" t="n">
-        <v>9</v>
+        <v>15495.24365234375</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>260</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>aten::copy_</t>
+          <t>aten::add</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>(8, 12, 64, 3137)</t>
+          <t>(1, 25089, 768)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+          <t>(1, 25089, 768)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>(2409216, 200768, 3137, 1)</t>
+          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>(7227648, 64, 1, 2304)</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0.019273728</v>
-      </c>
-      <c r="G3" t="n">
-        <v>73.5234375</v>
-      </c>
+          <t>(19268352, 768, 1)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>(19268352, 768, 1)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.25</v>
+        <v>0.019268352</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5011573421889868</v>
+        <v>110.25439453125</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5012429309440907</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0005911931389301384</v>
+        <v>3.116712998732709</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5003593038782586</v>
+        <v>3.086642791345411</v>
       </c>
       <c r="M3" t="n">
-        <v>0.501919680888061</v>
+        <v>0.1319357780554476</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1252893355472467</v>
+        <v>2.942040177141579</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1253107327360227</v>
+        <v>3.299371664334884</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0001477982847325346</v>
+        <v>0.5194521664554514</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1250898259695646</v>
+        <v>0.5144404652242351</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1254799202220153</v>
-      </c>
-      <c r="S3" t="inlineStr">
+        <v>0.02198929634257462</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.4903400295235965</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.5498952773891473</v>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>thread 17751 (python3)</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(1846.007), 'mean_duration_us': np.float64(153.83391666666668), 'median_duration_us': np.float64(153.8075), 'std_dev_duration_us': np.float64(0.17379991289475016), 'min_duration_us': np.float64(153.6), 'max_duration_us': np.float64(154.079)}]</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(153.83)}]</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>[[8, 12, 64, 3137], [8, 12, 64, 3137], []]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'gpu_op_uid': 47401, 'count': 24, 'total_duration_us': np.float64(891.774), 'mean_duration_us': np.float64(37.15725), 'median_duration_us': np.float64(37.471999999999994), 'std_dev_duration_us': np.float64(1.5359198723132224), 'min_duration_us': np.float64(35.04), 'max_duration_us': np.float64(39.296)}]</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(37.16)}]</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>[[1, 25089, 768], [1, 25089, 768], []]</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>[[2409216, 200768, 3137, 1], [7227648, 64, 1, 2304], []]</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>['', '', 'False']</t>
-        </is>
-      </c>
-      <c r="AC3" t="n">
-        <v>153.8339436848958</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>153.8074951171875</v>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>[[19268352, 768, 1], [19268352, 768, 1], []]</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>['', '', '1']</t>
+        </is>
       </c>
       <c r="AE3" t="n">
-        <v>0.1814923269919053</v>
+        <v>37.15723673502604</v>
       </c>
       <c r="AF3" t="n">
-        <v>153.60009765625</v>
+        <v>37.4720458984375</v>
       </c>
       <c r="AG3" t="n">
-        <v>154.0791015625</v>
+        <v>1.568952326542583</v>
       </c>
       <c r="AH3" t="n">
-        <v>1846.00732421875</v>
+        <v>35.0400390625</v>
       </c>
       <c r="AI3" t="n">
-        <v>12</v>
+        <v>39.2958984375</v>
       </c>
       <c r="AJ3" t="n">
-        <v>256</v>
+        <v>891.773681640625</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>324</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>aten::copy_</t>
+          <t>aten::add</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>(8, 12, 3137, 64)</t>
+          <t>(1, 25088, 768)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+          <t>(1, 25088, 768)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>(2409216, 200768, 64, 1)</t>
+          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>(7227648, 64, 2304, 1)</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>0.019273728</v>
-      </c>
-      <c r="G4" t="n">
-        <v>73.5234375</v>
-      </c>
+          <t>(19268352, 768, 1)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>(19267584, 768, 1)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.25</v>
+        <v>0.019267584</v>
       </c>
       <c r="I4" t="n">
-        <v>1.304559223068945</v>
+        <v>110.25</v>
       </c>
       <c r="J4" t="n">
-        <v>1.303000720317353</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01715970100611623</v>
+        <v>2.960838354303617</v>
       </c>
       <c r="L4" t="n">
-        <v>1.280159399496499</v>
+        <v>2.966065314624006</v>
       </c>
       <c r="M4" t="n">
-        <v>1.331060358927668</v>
+        <v>0.03684353277674083</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3261398057672362</v>
+        <v>2.894766682463412</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3257501800793383</v>
+        <v>3.008062308289448</v>
       </c>
       <c r="P4" t="n">
-        <v>0.004289925251529056</v>
+        <v>0.4934730590506029</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3200398498741249</v>
+        <v>0.4943442191040012</v>
       </c>
       <c r="R4" t="n">
-        <v>0.332765089731917</v>
-      </c>
-      <c r="S4" t="inlineStr">
+        <v>0.006140588796123471</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.482461113743902</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.5013437180482413</v>
+      </c>
+      <c r="U4" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>thread 17751 (python3)</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(1418.552), 'mean_duration_us': np.float64(59.10633333333333), 'median_duration_us': np.float64(59.167500000000004), 'std_dev_duration_us': np.float64(0.7604596563190504), 'min_duration_us': np.float64(57.92), 'max_duration_us': np.float64(60.223)}]</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(59.11)}]</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>[[8, 12, 3137, 64], [8, 12, 3137, 64], []]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt; &gt;(int, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt;, std::array&lt;char*, 3ul&gt;)', 'stream': 7, 'gpu_op_uid': 47301, 'count': 12, 'total_duration_us': np.float64(468.6050000000001), 'mean_duration_us': np.float64(39.05041666666667), 'median_duration_us': np.float64(38.976), 'std_dev_duration_us': np.float64(0.46841407222195597), 'min_duration_us': np.float64(38.432), 'max_duration_us': np.float64(39.936)}]</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::CU...', 'stream': 7, 'mean_duration_us': np.float64(39.05)}]</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>[[1, 25088, 768], [1, 25088, 768], []]</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>[[2409216, 200768, 64, 1], [7227648, 64, 2304, 1], []]</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>['', '', 'False']</t>
-        </is>
-      </c>
-      <c r="AC4" t="n">
-        <v>59.10631306966146</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>59.16748046875</v>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>[[19268352, 768, 1], [19267584, 768, 1], []]</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>['', '', '1']</t>
+        </is>
       </c>
       <c r="AE4" t="n">
-        <v>0.7768103961300407</v>
+        <v>39.05043538411459</v>
       </c>
       <c r="AF4" t="n">
-        <v>57.919921875</v>
+        <v>38.97607421875</v>
       </c>
       <c r="AG4" t="n">
-        <v>60.222900390625</v>
+        <v>0.4892606085061316</v>
       </c>
       <c r="AH4" t="n">
-        <v>1418.551513671875</v>
+        <v>38.431884765625</v>
       </c>
       <c r="AI4" t="n">
-        <v>24</v>
+        <v>39.93603515625</v>
       </c>
       <c r="AJ4" t="n">
-        <v>248</v>
+        <v>468.605224609375</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>aten::copy_</t>
+          <t>aten::add</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>(3136, 12, 8, 64)</t>
+          <t>(196, 128, 768)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+          <t>(1, 128, 768)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(6144, 512, 64, 1)</t>
+          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>(18432, 64, 2304, 1)</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
+          <t>(768, 151296, 1)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>(98304, 1, 128)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
         <v>0.019267584</v>
       </c>
-      <c r="G5" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.25</v>
-      </c>
       <c r="I5" t="n">
-        <v>1.321548671940372</v>
+        <v>73.6875</v>
       </c>
       <c r="J5" t="n">
-        <v>1.317717016856813</v>
+        <v>0.2493638676844784</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03358092858653137</v>
+        <v>0.897617029201552</v>
       </c>
       <c r="L5" t="n">
-        <v>1.281091233309661</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.362269598180649</v>
-      </c>
+        <v>0.897617029201552</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>0.330387167985093</v>
+        <v>0.897617029201552</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3294292542142033</v>
+        <v>0.897617029201552</v>
       </c>
       <c r="P5" t="n">
-        <v>0.008395232146632842</v>
+        <v>0.2238332541011504</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3202728083274152</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.3405673995451623</v>
-      </c>
-      <c r="S5" t="inlineStr">
+        <v>0.2238332541011504</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>0.2238332541011504</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.2238332541011504</v>
+      </c>
+      <c r="U5" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>thread 17751 (python3)</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 24, 'total_duration_us': np.float64(1400.504), 'mean_duration_us': np.float64(58.35433333333333), 'median_duration_us': np.float64(58.4955), 'std_dev_duration_us': np.float64(1.4517576320523424), 'min_duration_us': np.float64(56.575), 'max_duration_us': np.float64(60.16)}]</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(58.35)}]</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>[[3136, 12, 8, 64], [3136, 12, 8, 64], []]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 47201, 'count': 1, 'total_duration_us': np.float64(86.08), 'mean_duration_us': np.float64(86.08), 'median_duration_us': np.float64(86.08), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(86.08), 'max_duration_us': np.float64(86.08)}]</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(86.08)}]</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>[[196, 128, 768], [1, 128, 768], []]</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>[[6144, 512, 64, 1], [18432, 64, 2304, 1], []]</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>['', '', 'False']</t>
-        </is>
-      </c>
-      <c r="AC5" t="n">
-        <v>58.35430908203125</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>58.4954833984375</v>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>[[768, 151296, 1], [98304, 1, 128], []]</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>['', '', '1']</t>
+        </is>
       </c>
       <c r="AE5" t="n">
-        <v>1.483017836999234</v>
+        <v>86.080078125</v>
       </c>
       <c r="AF5" t="n">
-        <v>56.574951171875</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>60.159912109375</v>
-      </c>
+        <v>86.080078125</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>1400.50341796875</v>
+        <v>86.080078125</v>
       </c>
       <c r="AI5" t="n">
-        <v>24</v>
+        <v>86.080078125</v>
       </c>
       <c r="AJ5" t="n">
-        <v>112</v>
+        <v>86.080078125</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>aten::copy_</t>
+          <t>aten::add_</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>(3136, 8, 12, 64)</t>
+          <t>(128, 768, 14, 14)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+          <t>(1, 768, 1, 1)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>(6144, 768, 64, 1)</t>
+          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(6144, 64, 512, 1)</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
+          <t>(150528, 196, 14, 1)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>(768, 1, 1, 1)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
         <v>0.019267584</v>
       </c>
-      <c r="G6" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.25</v>
-      </c>
       <c r="I6" t="n">
-        <v>1.346541254451492</v>
+        <v>73.50146484375</v>
       </c>
       <c r="J6" t="n">
-        <v>1.346640415063802</v>
+        <v>0.249995017637563</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00649169023188425</v>
+        <v>1.188206952315353</v>
       </c>
       <c r="L6" t="n">
-        <v>1.335799292730712</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.35460602061431</v>
-      </c>
+        <v>1.188206952315353</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>0.3366353136128731</v>
+        <v>1.188206952315353</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3366601037659506</v>
+        <v>1.188206952315353</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001622922557971063</v>
+        <v>0.2970458180011518</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.333949823182678</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.3386515051535775</v>
-      </c>
-      <c r="S6" t="inlineStr">
+        <v>0.2970458180011518</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>0.2970458180011518</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.2970458180011518</v>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>thread 17751 (python3)</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(686.844), 'mean_duration_us': np.float64(57.237), 'median_duration_us': np.float64(57.2315), 'std_dev_duration_us': np.float64(0.2646696053573195), 'min_duration_us': np.float64(56.895), 'max_duration_us': np.float64(57.696)}]</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(57.24)}]</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>[[3136, 8, 12, 64], [3136, 8, 12, 64], []]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 47181, 'count': 1, 'total_duration_us': np.float64(64.864), 'mean_duration_us': np.float64(64.864), 'median_duration_us': np.float64(64.864), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(64.864), 'max_duration_us': np.float64(64.864)}]</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(64.86)}]</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>[[128, 768, 14, 14], [1, 768, 1, 1], []]</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>[[6144, 768, 64, 1], [6144, 64, 512, 1], []]</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>['', '', 'False']</t>
-        </is>
-      </c>
-      <c r="AC6" t="n">
-        <v>57.23699951171875</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>57.2315673828125</v>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>[[150528, 196, 14, 1], [768, 1, 1, 1], []]</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>['', '', '1']</t>
+        </is>
       </c>
       <c r="AE6" t="n">
-        <v>0.2764603445241264</v>
+        <v>64.864013671875</v>
       </c>
       <c r="AF6" t="n">
-        <v>56.89501953125</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>57.696044921875</v>
-      </c>
+        <v>64.864013671875</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="n">
-        <v>686.843994140625</v>
+        <v>64.864013671875</v>
       </c>
       <c r="AI6" t="n">
-        <v>12</v>
+        <v>64.864013671875</v>
       </c>
       <c r="AJ6" t="n">
-        <v>149</v>
+        <v>64.864013671875</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>aten::copy_</t>
+          <t>aten::mul</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>(8, 3137, 12, 64)</t>
+          <t>(3136, 12, 8, 8)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+          <t>()</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>(2409216, 768, 64, 1)</t>
+          <t>('c10::BFloat16', 'double', None)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>(2409216, 64, 200768, 1)</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>0.019273728</v>
-      </c>
-      <c r="G7" t="n">
-        <v>73.5234375</v>
-      </c>
+          <t>(768, 64, 8, 1)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>()</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>0.25</v>
+        <v>0.002408448</v>
       </c>
       <c r="I7" t="n">
-        <v>1.36424329615657</v>
+        <v>9.187507629394531</v>
       </c>
       <c r="J7" t="n">
-        <v>1.365007173751196</v>
+        <v>0.2499997923976001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.004485938567823921</v>
+        <v>1.913497870540554</v>
       </c>
       <c r="L7" t="n">
-        <v>1.354253462185379</v>
+        <v>1.942313683796023</v>
       </c>
       <c r="M7" t="n">
-        <v>1.371236835246147</v>
+        <v>0.08665362827660592</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3410608240391426</v>
+        <v>1.65416243135611</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3412517934377991</v>
+        <v>1.967689478408298</v>
       </c>
       <c r="P7" t="n">
-        <v>0.00112148464195598</v>
+        <v>0.4783740703883884</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3385633655463446</v>
+        <v>0.4855780177200236</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3428092088115369</v>
-      </c>
-      <c r="S7" t="inlineStr">
+        <v>0.02166338907965028</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.4135402644309369</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.4919219611050165</v>
+      </c>
+      <c r="U7" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>thread 17751 (python3)</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(678.1399999999999), 'mean_duration_us': np.float64(56.511666666666656), 'median_duration_us': np.float64(56.4795), 'std_dev_duration_us': np.float64(0.17831869098766825), 'min_duration_us': np.float64(56.223), 'max_duration_us': np.float64(56.928)}]</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(56.51)}]</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>[[8, 3137, 12, 64], [8, 3137, 12, 64], []]</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt; &gt;(int, at::native::AUnaryFunctor&lt;c10::BFloat16, c10::BFloat16, c10::BFloat16, at::native::binary_internal::MulFunctor&lt;float&gt; &gt;, std::array&lt;char*, 2ul&gt;)', 'stream': 7, 'gpu_op_uid': 47247, 'count': 12, 'total_duration_us': np.float64(60.544), 'mean_duration_us': np.float64(5.045333333333333), 'median_duration_us': np.float64(4.96), 'std_dev_duration_us': np.float64(0.24591236017916807), 'min_duration_us': np.float64(4.896), 'max_duration_us': np.float64(5.824)}]</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
+          <t>[{'name': 'void at::native::vectorized_elementwise_kernel&lt;4, at::native::AU...', 'stream': 7, 'mean_duration_us': np.float64(5.05)}]</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>[[2409216, 768, 64, 1], [2409216, 64, 200768, 1], []]</t>
+          <t>[[3136, 12, 8, 8], []]</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>['', '', 'False']</t>
-        </is>
-      </c>
-      <c r="AC7" t="n">
-        <v>56.51167805989584</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>56.4794921875</v>
+          <t>['c10::BFloat16', 'double']</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>[[768, 64, 8, 1], []]</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>['', '']</t>
+        </is>
       </c>
       <c r="AE7" t="n">
-        <v>0.1862679325817069</v>
+        <v>5.045308430989583</v>
       </c>
       <c r="AF7" t="n">
-        <v>56.222900390625</v>
+        <v>4.9599609375</v>
       </c>
       <c r="AG7" t="n">
-        <v>56.927978515625</v>
+        <v>0.25685255038906</v>
       </c>
       <c r="AH7" t="n">
-        <v>678.14013671875</v>
+        <v>4.89599609375</v>
       </c>
       <c r="AI7" t="n">
+        <v>5.823974609375</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>60.543701171875</v>
+      </c>
+      <c r="AK7" t="n">
         <v>12</v>
       </c>
-      <c r="AJ7" t="n">
-        <v>285</v>
+      <c r="AL7" t="n">
+        <v>124</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>aten::copy_</t>
+          <t>aten::add</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>(1, 224, 14, 8, 768)</t>
+          <t>(128, 197, 768)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
+          <t>(1, 197, 768)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>(19267584, 86016, 6144, 768, 1)</t>
+          <t>('c10::BFloat16', 'c10::BFloat16', None)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>(19273728, 10752, 768, 2409216, 1)</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>0.019267584</v>
-      </c>
-      <c r="G8" t="n">
-        <v>73.5</v>
-      </c>
+          <t>(151296, 768, 1)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>(151296, 768, 1)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>0.25</v>
+        <v>0.019365888</v>
       </c>
       <c r="I8" t="n">
-        <v>1.449765337831095</v>
+        <v>74.16357421875</v>
       </c>
       <c r="J8" t="n">
-        <v>1.449124642695606</v>
+        <v>0.2490272373540856</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008992930670082923</v>
+        <v>1.440569687238257</v>
       </c>
       <c r="L8" t="n">
-        <v>1.436162906973359</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.464105115442947</v>
-      </c>
+        <v>1.440569687238257</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>0.3624413344577738</v>
+        <v>1.440569687238257</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3622811606739015</v>
+        <v>1.440569687238257</v>
       </c>
       <c r="P8" t="n">
-        <v>0.002248232667520731</v>
+        <v>0.3587410894289824</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3590407267433396</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.3660262788607366</v>
-      </c>
-      <c r="S8" t="inlineStr">
+        <v>0.3587410894289824</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>0.3587410894289824</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.3587410894289824</v>
+      </c>
+      <c r="U8" t="inlineStr">
         <is>
           <t>python3</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>CPU</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>thread 17751 (python3)</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>vector_bf16</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(637.9490000000001), 'mean_duration_us': np.float64(53.16241666666667), 'median_duration_us': np.float64(53.184), 'std_dev_duration_us': np.float64(0.31582021740576044), 'min_duration_us': np.float64(52.64), 'max_duration_us': np.float64(53.664)}]</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(53.16)}]</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>[[1, 224, 14, 8, 768], [1, 224, 14, 8, 768], []]</t>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; &gt;(at::TensorIteratorBase&amp;, at::native::CUDAFunctor_add&lt;c10::BFloat16&gt; const&amp;)::{lambda(int)#1})', 'stream': 7, 'gpu_op_uid': 47189, 'count': 1, 'total_duration_us': np.float64(53.983), 'mean_duration_us': np.float64(53.983), 'median_duration_us': np.float64(53.983), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(53.983), 'max_duration_us': np.float64(53.983)}]</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
+          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(53.98)}]</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>[[128, 197, 768], [1, 197, 768], []]</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>[[19267584, 86016, 6144, 768, 1], [19273728, 10752, 768, 2409216, 1], []]</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>['', '', 'False']</t>
-        </is>
-      </c>
-      <c r="AC8" t="n">
-        <v>53.16243489583334</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>53.18408203125</v>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>[[151296, 768, 1], [151296, 768, 1], []]</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>['', '', '1']</t>
+        </is>
       </c>
       <c r="AE8" t="n">
-        <v>0.3298869750019682</v>
+        <v>53.98291015625</v>
       </c>
       <c r="AF8" t="n">
-        <v>52.639892578125</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>53.6640625</v>
-      </c>
+        <v>53.98291015625</v>
+      </c>
+      <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="n">
-        <v>637.94921875</v>
+        <v>53.98291015625</v>
       </c>
       <c r="AI8" t="n">
-        <v>12</v>
+        <v>53.98291015625</v>
       </c>
       <c r="AJ8" t="n">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>aten::copy_</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>(3136, 12, 64, 8)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>(6144, 512, 8, 1)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>(18432, 64, 1, 2304)</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>0.019267584</v>
-      </c>
-      <c r="G9" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.509537166523619</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.509539221380834</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.01116693498626933</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.493149131610688</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.526292843599513</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.3773842916309048</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.3773848053452085</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.002791733746567333</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.373287282902672</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.3815732108998782</v>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>python3</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>thread 17751 (python3)</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>vector_bf16</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(612.698), 'mean_duration_us': np.float64(51.058166666666665), 'median_duration_us': np.float64(51.055499999999995), 'std_dev_duration_us': np.float64(0.36143575577902604), 'min_duration_us': np.float64(50.495), 'max_duration_us': np.float64(51.616)}]</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(51.06)}]</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>[[3136, 12, 64, 8], [3136, 12, 64, 8], []]</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>[[6144, 512, 8, 1], [18432, 64, 1, 2304], []]</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>['', '', 'False']</t>
-        </is>
-      </c>
-      <c r="AC9" t="n">
-        <v>51.05816650390625</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>51.0555419921875</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0.3774848472435202</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>50.4951171875</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>51.615966796875</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>612.697998046875</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>aten::copy_</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>(1, 196, 128, 768)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>(19267584, 98304, 768, 1)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>(150528, 768, 150528, 1)</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>0.019267584</v>
-      </c>
-      <c r="G10" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.489457525164785</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.489457525164785</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
-        <v>1.489457525164785</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.489457525164785</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.3723643812911963</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.3723643812911963</v>
-      </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="n">
-        <v>0.3723643812911963</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.3723643812911963</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>python3</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>thread 17751 (python3)</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>vector_bf16</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(51.744), 'mean_duration_us': np.float64(51.744), 'median_duration_us': np.float64(51.744), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(51.744), 'max_duration_us': np.float64(51.744)}]</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(51.74)}]</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>[[1, 196, 128, 768], [1, 196, 128, 768], []]</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>[[19267584, 98304, 768, 1], [150528, 768, 150528, 1], []]</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>['', '', 'False']</t>
-        </is>
-      </c>
-      <c r="AC10" t="n">
-        <v>51.743896484375</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>51.743896484375</v>
-      </c>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="n">
-        <v>51.743896484375</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>51.743896484375</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>51.743896484375</v>
-      </c>
-      <c r="AI10" t="n">
+        <v>53.98291015625</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1</v>
       </c>
-      <c r="AJ10" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>aten::copy_</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>(1, 8, 1, 1, 1, 768)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>(6144, 768, 768, 6144, 768, 1)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>(0, 0, 19268352, 19268352, 768, 1)</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>6.144e-06</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.0234375</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.007097606117564984</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.006981779442363712</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.0004125868896499309</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.006736935885423638</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.008347565801476076</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.001774401529391246</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.001745444860590928</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.0001031467224124827</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.00168423397135591</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.002086891450369019</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>python3</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>thread 17751 (python3)</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>vector_bf16</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 12, 'total_duration_us': np.float64(41.66400000000001), 'mean_duration_us': np.float64(3.472000000000001), 'median_duration_us': np.float64(3.52), 'std_dev_duration_us': np.float64(0.17008233300375442), 'min_duration_us': np.float64(2.944), 'max_duration_us': np.float64(3.648)}]</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(3.47)}]</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>[[1, 8, 1, 1, 1, 768], [1, 8, 1, 1, 1, 768], []]</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>[[6144, 768, 768, 6144, 768, 1], [0, 0, 19268352, 19268352, 768, 1], []]</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>['', '', 'False']</t>
-        </is>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.472025553385417</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>3.52001953125</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0.17761358856306</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.944091796875</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>3.64794921875</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>41.664306640625</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>aten::copy_</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>(1, 768, 8)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>(6144, 8, 1)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>(6144, 1, 768)</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>6.144e-06</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.0234375</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.006145500366300367</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.006145500366300367</v>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="n">
-        <v>0.006145500366300367</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.006145500366300367</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.001536375091575092</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.001536375091575092</v>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="n">
-        <v>0.001536375091575092</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.001536375091575092</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>python3</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>thread 17751 (python3)</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>vector_bf16</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1}&gt;(int, at::native::gpu_kernel_impl_nocast&lt;at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1}&gt;(at::TensorIteratorBase&amp;, at::native::direct_copy_kernel_cuda(at::TensorIteratorBase&amp;)::{lambda()#3}::operator()() const::{lambda()#12}::operator()() const::{lambda(c10::BFloat16)#1} const&amp;)::{lambda(int)#1})', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(3.999), 'mean_duration_us': np.float64(3.999), 'median_duration_us': np.float64(3.999), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(3.999), 'max_duration_us': np.float64(3.999)}]</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>[{'name': 'void at::native::elementwise_kernel&lt;128, 4, at::native::gpu_kern...', 'stream': 7, 'mean_duration_us': np.float64(4.0)}]</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>[[1, 768, 8], [1, 768, 8], []]</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>[[6144, 8, 1], [6144, 1, 768], []]</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>['', '', 'False']</t>
-        </is>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.9990234375</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.9990234375</v>
-      </c>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="n">
-        <v>3.9990234375</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>3.9990234375</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>3.9990234375</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>aten::copy_</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>(1, 400)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>('c10::BFloat16', 'c10::BFloat16')</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>(400, 1)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>(400, 1)</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>4e-07</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.00152587890625</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.0005747259493115847</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.0005747259493115847</v>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="n">
-        <v>0.0005747259493115847</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.0005747259493115847</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.0001436814873278962</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.0001436814873278962</v>
-      </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="n">
-        <v>0.0001436814873278962</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.0001436814873278962</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>python3</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>thread 17751 (python3)</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>vector_bf16</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'count': 1, 'total_duration_us': np.float64(2.784), 'mean_duration_us': np.float64(2.784), 'median_duration_us': np.float64(2.784), 'std_dev_duration_us': np.float64(0.0), 'min_duration_us': np.float64(2.784), 'max_duration_us': np.float64(2.784)}]</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>[{'name': 'Memcpy DtoH (Device -&gt; Pageable)', 'stream': 7, 'mean_duration_us': np.float64(2.78)}]</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>[[1, 400], [1, 400], []]</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>['c10::BFloat16', 'c10::BFloat16', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>[[400, 1], [400, 1], []]</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>['', '', 'False']</t>
-        </is>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.783935546875</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.783935546875</v>
-      </c>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="n">
-        <v>2.783935546875</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.783935546875</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>2.783935546875</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>3531</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>aten::copy_</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>(1, 128, 3, 224, 224)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>('c10::BFloat16', 'float')</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>(19267584, 150528, 50176, 224, 1)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>(19267584, 150528, 50176, 224, 1)</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>0.019267584</v>
-      </c>
-      <c r="G14" t="n">
-        <v>110.25</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>python3</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>thread 17751 (python3)</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>vector_bf16</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>[[1, 128, 3, 224, 224], [1, 128, 3, 224, 224], []]</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>['c10::BFloat16', 'float', 'Scalar']</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>[[19267584, 150528, 50176, 224, 1], [19267584, 150528, 50176, 224, 1], []]</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>['', '', 'False']</t>
-        </is>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>5</v>
+      <c r="AL8" t="n">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
